--- a/src/main/resources/templates/summaryReportForm2.xlsx
+++ b/src/main/resources/templates/summaryReportForm2.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21231"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{15FAB809-F80C-4DDD-8B37-6445C3BEE8DA}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C884BDB4-FEA3-4A43-AF6C-3E6D79A24E33}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -541,58 +541,61 @@
     <t>$dist_pct_value73_value72</t>
   </si>
   <si>
-    <t>$dist_prd_value71_value89</t>
-  </si>
-  <si>
-    <t>$dist_prd_value72_value90</t>
-  </si>
-  <si>
-    <t>$dist_prd_value73_value81</t>
-  </si>
-  <si>
-    <t>$dist_prd_value77_value76</t>
-  </si>
-  <si>
-    <t>$dist_prd_value3_value2</t>
-  </si>
-  <si>
-    <t>$dist_prd_value6_value5</t>
-  </si>
-  <si>
-    <t>$dist_prd_value9_value8</t>
-  </si>
-  <si>
-    <t>$dist_prd_value12_value11</t>
-  </si>
-  <si>
-    <t>$dist_prd_value18_value17</t>
-  </si>
-  <si>
-    <t>$dist_prd_value21_value20</t>
-  </si>
-  <si>
-    <t>$dist_prd_value24_value23</t>
-  </si>
-  <si>
-    <t>$dist_prd_value30_value29</t>
-  </si>
-  <si>
-    <t>$dist_prd_value33_value32</t>
-  </si>
-  <si>
-    <t>$header_lastYear</t>
-  </si>
-  <si>
-    <t>$header_year</t>
-  </si>
-  <si>
-    <t>$header_reportDate</t>
+    <t>$dist_pct_value77_value76</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value3_value2</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value6_value5</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value9_value8</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value12_value11</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value18_value17</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value21_value20</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value24_value23</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value30_value29</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value33_value32</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value71_value89</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value72_value90</t>
+  </si>
+  <si>
+    <t>$dist_pdc_value73_value81</t>
+  </si>
+  <si>
+    <t>$cell_reportDate</t>
+  </si>
+  <si>
+    <t>$cell_lastYear</t>
+  </si>
+  <si>
+    <t>$cell_year</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <numFmts count="1">
+    <numFmt numFmtId="164" formatCode="0.0"/>
+  </numFmts>
   <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
@@ -766,7 +769,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="32">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
@@ -811,53 +814,47 @@
     <xf numFmtId="49" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center"/>
     </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="1" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="2" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1149,18 +1146,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="C1" s="25" t="s">
+      <c r="C1" s="24" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="25"/>
-      <c r="E1" s="25"/>
-      <c r="F1" s="25"/>
-      <c r="G1" s="25"/>
-      <c r="H1" s="25"/>
-      <c r="I1" s="25"/>
-      <c r="J1" s="25"/>
-      <c r="K1" s="25"/>
-      <c r="L1" s="25"/>
+      <c r="D1" s="24"/>
+      <c r="E1" s="24"/>
+      <c r="F1" s="24"/>
+      <c r="G1" s="24"/>
+      <c r="H1" s="24"/>
+      <c r="I1" s="24"/>
+      <c r="J1" s="24"/>
+      <c r="K1" s="24"/>
+      <c r="L1" s="24"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
@@ -1202,17 +1199,17 @@
       <c r="AY1" s="1"/>
     </row>
     <row r="2" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="C2" s="25" t="s">
+      <c r="C2" s="24" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="25"/>
-      <c r="E2" s="25"/>
-      <c r="F2" s="25"/>
-      <c r="G2" s="25"/>
-      <c r="H2" s="25"/>
-      <c r="I2" s="25"/>
-      <c r="J2" s="25"/>
-      <c r="K2" s="25"/>
+      <c r="D2" s="24"/>
+      <c r="E2" s="24"/>
+      <c r="F2" s="24"/>
+      <c r="G2" s="24"/>
+      <c r="H2" s="24"/>
+      <c r="I2" s="24"/>
+      <c r="J2" s="24"/>
+      <c r="K2" s="24"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
@@ -1260,208 +1257,208 @@
         <v>2</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
     </row>
     <row r="5" spans="1:73" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="26" t="s">
+      <c r="A5" s="23" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="26" t="s">
+      <c r="B5" s="23" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="28" t="s">
+      <c r="C5" s="26" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="28"/>
-      <c r="E5" s="28"/>
-      <c r="F5" s="28"/>
-      <c r="G5" s="29" t="s">
+      <c r="D5" s="26"/>
+      <c r="E5" s="26"/>
+      <c r="F5" s="26"/>
+      <c r="G5" s="20" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="29"/>
-      <c r="I5" s="29"/>
-      <c r="J5" s="29"/>
-      <c r="K5" s="29"/>
-      <c r="L5" s="29"/>
-      <c r="M5" s="29"/>
-      <c r="N5" s="29"/>
-      <c r="O5" s="29"/>
-      <c r="P5" s="29"/>
-      <c r="Q5" s="29"/>
-      <c r="R5" s="29"/>
-      <c r="S5" s="29"/>
-      <c r="T5" s="29"/>
-      <c r="U5" s="29"/>
-      <c r="V5" s="29"/>
-      <c r="W5" s="29"/>
-      <c r="X5" s="29"/>
-      <c r="Y5" s="29"/>
-      <c r="Z5" s="29"/>
-      <c r="AA5" s="29"/>
-      <c r="AB5" s="33" t="s">
+      <c r="H5" s="20"/>
+      <c r="I5" s="20"/>
+      <c r="J5" s="20"/>
+      <c r="K5" s="20"/>
+      <c r="L5" s="20"/>
+      <c r="M5" s="20"/>
+      <c r="N5" s="20"/>
+      <c r="O5" s="20"/>
+      <c r="P5" s="20"/>
+      <c r="Q5" s="20"/>
+      <c r="R5" s="20"/>
+      <c r="S5" s="20"/>
+      <c r="T5" s="20"/>
+      <c r="U5" s="20"/>
+      <c r="V5" s="20"/>
+      <c r="W5" s="20"/>
+      <c r="X5" s="20"/>
+      <c r="Y5" s="20"/>
+      <c r="Z5" s="20"/>
+      <c r="AA5" s="20"/>
+      <c r="AB5" s="19" t="s">
         <v>7</v>
       </c>
-      <c r="AC5" s="33"/>
-      <c r="AD5" s="33"/>
-      <c r="AE5" s="29" t="s">
+      <c r="AC5" s="19"/>
+      <c r="AD5" s="19"/>
+      <c r="AE5" s="20" t="s">
         <v>8</v>
       </c>
-      <c r="AF5" s="29"/>
-      <c r="AG5" s="29"/>
-      <c r="AH5" s="32" t="s">
+      <c r="AF5" s="20"/>
+      <c r="AG5" s="20"/>
+      <c r="AH5" s="21" t="s">
         <v>9</v>
       </c>
-      <c r="AI5" s="32"/>
-      <c r="AJ5" s="32"/>
-      <c r="AK5" s="32"/>
-      <c r="AL5" s="32"/>
-      <c r="AM5" s="32"/>
-      <c r="AN5" s="32"/>
-      <c r="AO5" s="32"/>
-      <c r="AP5" s="32"/>
-      <c r="AQ5" s="32"/>
-      <c r="AR5" s="32"/>
-      <c r="AS5" s="32"/>
-      <c r="AT5" s="32"/>
-      <c r="AU5" s="32"/>
-      <c r="AV5" s="32"/>
-      <c r="AW5" s="32"/>
-      <c r="AX5" s="32"/>
-      <c r="AY5" s="32"/>
-      <c r="AZ5" s="32"/>
-      <c r="BA5" s="32"/>
-      <c r="BB5" s="32"/>
-      <c r="BC5" s="32"/>
-      <c r="BD5" s="32"/>
-      <c r="BE5" s="32"/>
-      <c r="BF5" s="32"/>
-      <c r="BG5" s="32"/>
-      <c r="BH5" s="32"/>
-      <c r="BI5" s="32"/>
-      <c r="BJ5" s="32"/>
-      <c r="BK5" s="32"/>
-      <c r="BL5" s="32" t="s">
+      <c r="AI5" s="21"/>
+      <c r="AJ5" s="21"/>
+      <c r="AK5" s="21"/>
+      <c r="AL5" s="21"/>
+      <c r="AM5" s="21"/>
+      <c r="AN5" s="21"/>
+      <c r="AO5" s="21"/>
+      <c r="AP5" s="21"/>
+      <c r="AQ5" s="21"/>
+      <c r="AR5" s="21"/>
+      <c r="AS5" s="21"/>
+      <c r="AT5" s="21"/>
+      <c r="AU5" s="21"/>
+      <c r="AV5" s="21"/>
+      <c r="AW5" s="21"/>
+      <c r="AX5" s="21"/>
+      <c r="AY5" s="21"/>
+      <c r="AZ5" s="21"/>
+      <c r="BA5" s="21"/>
+      <c r="BB5" s="21"/>
+      <c r="BC5" s="21"/>
+      <c r="BD5" s="21"/>
+      <c r="BE5" s="21"/>
+      <c r="BF5" s="21"/>
+      <c r="BG5" s="21"/>
+      <c r="BH5" s="21"/>
+      <c r="BI5" s="21"/>
+      <c r="BJ5" s="21"/>
+      <c r="BK5" s="21"/>
+      <c r="BL5" s="21" t="s">
         <v>10</v>
       </c>
-      <c r="BM5" s="32"/>
-      <c r="BN5" s="32"/>
-      <c r="BO5" s="32"/>
-      <c r="BP5" s="32"/>
-      <c r="BQ5" s="32"/>
-      <c r="BR5" s="32"/>
-      <c r="BS5" s="32"/>
-      <c r="BT5" s="31" t="s">
+      <c r="BM5" s="21"/>
+      <c r="BN5" s="21"/>
+      <c r="BO5" s="21"/>
+      <c r="BP5" s="21"/>
+      <c r="BQ5" s="21"/>
+      <c r="BR5" s="21"/>
+      <c r="BS5" s="21"/>
+      <c r="BT5" s="22" t="s">
         <v>11</v>
       </c>
-      <c r="BU5" s="31" t="s">
+      <c r="BU5" s="22" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:73" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="26"/>
-      <c r="B6" s="26"/>
-      <c r="C6" s="28"/>
-      <c r="D6" s="28"/>
-      <c r="E6" s="28"/>
-      <c r="F6" s="28"/>
-      <c r="G6" s="29" t="s">
+      <c r="A6" s="23"/>
+      <c r="B6" s="23"/>
+      <c r="C6" s="26"/>
+      <c r="D6" s="26"/>
+      <c r="E6" s="26"/>
+      <c r="F6" s="26"/>
+      <c r="G6" s="20" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="29"/>
-      <c r="I6" s="29"/>
-      <c r="J6" s="29"/>
-      <c r="K6" s="29"/>
-      <c r="L6" s="29"/>
-      <c r="M6" s="29"/>
-      <c r="N6" s="29"/>
-      <c r="O6" s="29"/>
-      <c r="P6" s="29"/>
-      <c r="Q6" s="29"/>
-      <c r="R6" s="29"/>
-      <c r="S6" s="29" t="s">
+      <c r="H6" s="20"/>
+      <c r="I6" s="20"/>
+      <c r="J6" s="20"/>
+      <c r="K6" s="20"/>
+      <c r="L6" s="20"/>
+      <c r="M6" s="20"/>
+      <c r="N6" s="20"/>
+      <c r="O6" s="20"/>
+      <c r="P6" s="20"/>
+      <c r="Q6" s="20"/>
+      <c r="R6" s="20"/>
+      <c r="S6" s="20" t="s">
         <v>14</v>
       </c>
-      <c r="T6" s="29"/>
-      <c r="U6" s="29"/>
-      <c r="V6" s="29"/>
-      <c r="W6" s="29"/>
-      <c r="X6" s="29"/>
-      <c r="Y6" s="29"/>
-      <c r="Z6" s="29"/>
-      <c r="AA6" s="29"/>
-      <c r="AB6" s="33"/>
-      <c r="AC6" s="33"/>
-      <c r="AD6" s="33"/>
-      <c r="AE6" s="29"/>
-      <c r="AF6" s="29"/>
-      <c r="AG6" s="29"/>
-      <c r="AH6" s="32" t="s">
+      <c r="T6" s="20"/>
+      <c r="U6" s="20"/>
+      <c r="V6" s="20"/>
+      <c r="W6" s="20"/>
+      <c r="X6" s="20"/>
+      <c r="Y6" s="20"/>
+      <c r="Z6" s="20"/>
+      <c r="AA6" s="20"/>
+      <c r="AB6" s="19"/>
+      <c r="AC6" s="19"/>
+      <c r="AD6" s="19"/>
+      <c r="AE6" s="20"/>
+      <c r="AF6" s="20"/>
+      <c r="AG6" s="20"/>
+      <c r="AH6" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="AI6" s="32"/>
-      <c r="AJ6" s="32"/>
-      <c r="AK6" s="32"/>
-      <c r="AL6" s="32" t="s">
+      <c r="AI6" s="21"/>
+      <c r="AJ6" s="21"/>
+      <c r="AK6" s="21"/>
+      <c r="AL6" s="21" t="s">
         <v>16</v>
       </c>
-      <c r="AM6" s="32"/>
-      <c r="AN6" s="32"/>
-      <c r="AO6" s="32"/>
-      <c r="AP6" s="32" t="s">
+      <c r="AM6" s="21"/>
+      <c r="AN6" s="21"/>
+      <c r="AO6" s="21"/>
+      <c r="AP6" s="21" t="s">
         <v>17</v>
       </c>
-      <c r="AQ6" s="32"/>
-      <c r="AR6" s="32"/>
-      <c r="AS6" s="32"/>
-      <c r="AT6" s="32" t="s">
+      <c r="AQ6" s="21"/>
+      <c r="AR6" s="21"/>
+      <c r="AS6" s="21"/>
+      <c r="AT6" s="21" t="s">
         <v>18</v>
       </c>
-      <c r="AU6" s="32"/>
-      <c r="AV6" s="32"/>
-      <c r="AW6" s="32"/>
-      <c r="AX6" s="32" t="s">
+      <c r="AU6" s="21"/>
+      <c r="AV6" s="21"/>
+      <c r="AW6" s="21"/>
+      <c r="AX6" s="21" t="s">
         <v>19</v>
       </c>
-      <c r="AY6" s="32"/>
-      <c r="AZ6" s="32"/>
-      <c r="BA6" s="32"/>
-      <c r="BB6" s="26" t="s">
+      <c r="AY6" s="21"/>
+      <c r="AZ6" s="21"/>
+      <c r="BA6" s="21"/>
+      <c r="BB6" s="23" t="s">
         <v>20</v>
       </c>
-      <c r="BC6" s="26" t="s">
+      <c r="BC6" s="23" t="s">
         <v>21</v>
       </c>
-      <c r="BD6" s="32" t="s">
+      <c r="BD6" s="21" t="s">
         <v>22</v>
       </c>
-      <c r="BE6" s="32"/>
-      <c r="BF6" s="32"/>
-      <c r="BG6" s="32"/>
-      <c r="BH6" s="32" t="s">
+      <c r="BE6" s="21"/>
+      <c r="BF6" s="21"/>
+      <c r="BG6" s="21"/>
+      <c r="BH6" s="21" t="s">
         <v>23</v>
       </c>
-      <c r="BI6" s="32"/>
-      <c r="BJ6" s="32"/>
-      <c r="BK6" s="32"/>
-      <c r="BL6" s="32" t="s">
+      <c r="BI6" s="21"/>
+      <c r="BJ6" s="21"/>
+      <c r="BK6" s="21"/>
+      <c r="BL6" s="21" t="s">
         <v>24</v>
       </c>
-      <c r="BM6" s="32"/>
-      <c r="BN6" s="32"/>
-      <c r="BO6" s="32"/>
-      <c r="BP6" s="32" t="s">
+      <c r="BM6" s="21"/>
+      <c r="BN6" s="21"/>
+      <c r="BO6" s="21"/>
+      <c r="BP6" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="BQ6" s="32"/>
-      <c r="BR6" s="32"/>
-      <c r="BS6" s="32"/>
-      <c r="BT6" s="31"/>
-      <c r="BU6" s="31"/>
+      <c r="BQ6" s="21"/>
+      <c r="BR6" s="21"/>
+      <c r="BS6" s="21"/>
+      <c r="BT6" s="22"/>
+      <c r="BU6" s="22"/>
     </row>
     <row r="7" spans="1:73" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="26"/>
-      <c r="B7" s="26"/>
+      <c r="A7" s="23"/>
+      <c r="B7" s="23"/>
       <c r="C7" s="7" t="s">
         <v>26</v>
       </c>
@@ -1472,47 +1469,47 @@
         <v>28</v>
       </c>
       <c r="F7" s="8"/>
-      <c r="G7" s="30" t="s">
+      <c r="G7" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="30"/>
-      <c r="I7" s="30"/>
-      <c r="J7" s="30" t="s">
+      <c r="H7" s="27"/>
+      <c r="I7" s="27"/>
+      <c r="J7" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="K7" s="30"/>
-      <c r="L7" s="30"/>
-      <c r="M7" s="30" t="s">
+      <c r="K7" s="27"/>
+      <c r="L7" s="27"/>
+      <c r="M7" s="27" t="s">
         <v>31</v>
       </c>
-      <c r="N7" s="30"/>
-      <c r="O7" s="30"/>
-      <c r="P7" s="30" t="s">
+      <c r="N7" s="27"/>
+      <c r="O7" s="27"/>
+      <c r="P7" s="27" t="s">
         <v>32</v>
       </c>
-      <c r="Q7" s="30"/>
-      <c r="R7" s="30"/>
-      <c r="S7" s="30" t="s">
+      <c r="Q7" s="27"/>
+      <c r="R7" s="27"/>
+      <c r="S7" s="27" t="s">
         <v>29</v>
       </c>
-      <c r="T7" s="30"/>
-      <c r="U7" s="30"/>
-      <c r="V7" s="30" t="s">
+      <c r="T7" s="27"/>
+      <c r="U7" s="27"/>
+      <c r="V7" s="27" t="s">
         <v>30</v>
       </c>
-      <c r="W7" s="30"/>
-      <c r="X7" s="30"/>
-      <c r="Y7" s="30" t="s">
+      <c r="W7" s="27"/>
+      <c r="X7" s="27"/>
+      <c r="Y7" s="27" t="s">
         <v>33</v>
       </c>
-      <c r="Z7" s="30"/>
-      <c r="AA7" s="30"/>
-      <c r="AB7" s="33"/>
-      <c r="AC7" s="33"/>
-      <c r="AD7" s="33"/>
-      <c r="AE7" s="29"/>
-      <c r="AF7" s="29"/>
-      <c r="AG7" s="29"/>
+      <c r="Z7" s="27"/>
+      <c r="AA7" s="27"/>
+      <c r="AB7" s="19"/>
+      <c r="AC7" s="19"/>
+      <c r="AD7" s="19"/>
+      <c r="AE7" s="20"/>
+      <c r="AF7" s="20"/>
+      <c r="AG7" s="20"/>
       <c r="AH7" s="7" t="s">
         <v>26</v>
       </c>
@@ -1563,8 +1560,8 @@
         <v>28</v>
       </c>
       <c r="BA7" s="9"/>
-      <c r="BB7" s="26"/>
-      <c r="BC7" s="26"/>
+      <c r="BB7" s="23"/>
+      <c r="BC7" s="23"/>
       <c r="BD7" s="7" t="s">
         <v>34</v>
       </c>
@@ -1613,16 +1610,16 @@
       </c>
     </row>
     <row r="8" spans="1:73" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="27"/>
-      <c r="B8" s="27"/>
+      <c r="A8" s="25"/>
+      <c r="B8" s="25"/>
       <c r="C8" s="12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="D8" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="E8" s="13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="F8" s="14" t="s">
         <v>36</v>
@@ -1709,125 +1706,125 @@
         <v>39</v>
       </c>
       <c r="AH8" s="12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AI8" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AJ8" s="13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AK8" s="14" t="s">
         <v>36</v>
       </c>
       <c r="AL8" s="12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AM8" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AN8" s="13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AO8" s="14" t="s">
         <v>36</v>
       </c>
       <c r="AP8" s="12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AQ8" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AR8" s="13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AS8" s="14" t="s">
         <v>36</v>
       </c>
       <c r="AT8" s="12" t="str">
         <f>$C$8</f>
-        <v>$header_lastYear</v>
+        <v>$cell_lastYear</v>
       </c>
       <c r="AU8" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AV8" s="13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AW8" s="14" t="s">
         <v>36</v>
       </c>
       <c r="AX8" s="12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="AY8" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="AZ8" s="13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="BA8" s="14" t="s">
         <v>36</v>
       </c>
       <c r="BB8" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="BC8" s="13" t="s">
+        <v>188</v>
+      </c>
+      <c r="BD8" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="BC8" s="13" t="s">
-        <v>187</v>
-      </c>
-      <c r="BD8" s="12" t="s">
-        <v>186</v>
-      </c>
       <c r="BE8" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="BF8" s="13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="BG8" s="14" t="s">
         <v>36</v>
       </c>
       <c r="BH8" s="12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="BI8" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="BJ8" s="13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="BK8" s="14" t="s">
         <v>36</v>
       </c>
       <c r="BL8" s="12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="BM8" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="BN8" s="13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="BO8" s="14" t="s">
         <v>36</v>
       </c>
       <c r="BP8" s="12" t="s">
-        <v>186</v>
+        <v>187</v>
       </c>
       <c r="BQ8" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="BR8" s="13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="BS8" s="14" t="s">
         <v>36</v>
       </c>
       <c r="BT8" s="12" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
       <c r="BU8" s="13" t="s">
-        <v>187</v>
+        <v>188</v>
       </c>
     </row>
     <row r="9" spans="1:73" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
@@ -1835,460 +1832,443 @@
         <v>90</v>
       </c>
       <c r="B9" s="17"/>
-      <c r="C9" s="18" t="s">
+      <c r="C9" s="28" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="18" t="s">
+      <c r="D9" s="28" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="18" t="s">
+      <c r="E9" s="28" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="19" t="s">
+      <c r="F9" s="28" t="s">
         <v>164</v>
       </c>
-      <c r="G9" s="18" t="s">
+      <c r="G9" s="28" t="s">
         <v>44</v>
       </c>
-      <c r="H9" s="18" t="s">
+      <c r="H9" s="28" t="s">
         <v>45</v>
       </c>
-      <c r="I9" s="19" t="s">
+      <c r="I9" s="28" t="s">
+        <v>174</v>
+      </c>
+      <c r="J9" s="28" t="s">
+        <v>46</v>
+      </c>
+      <c r="K9" s="28" t="s">
+        <v>47</v>
+      </c>
+      <c r="L9" s="28" t="s">
+        <v>175</v>
+      </c>
+      <c r="M9" s="28" t="s">
+        <v>48</v>
+      </c>
+      <c r="N9" s="28" t="s">
+        <v>49</v>
+      </c>
+      <c r="O9" s="28" t="s">
+        <v>176</v>
+      </c>
+      <c r="P9" s="28" t="s">
+        <v>50</v>
+      </c>
+      <c r="Q9" s="28" t="s">
+        <v>51</v>
+      </c>
+      <c r="R9" s="28" t="s">
         <v>177</v>
       </c>
-      <c r="J9" s="18" t="s">
-        <v>46</v>
-      </c>
-      <c r="K9" s="18" t="s">
-        <v>47</v>
-      </c>
-      <c r="L9" s="19" t="s">
+      <c r="S9" s="28" t="s">
+        <v>52</v>
+      </c>
+      <c r="T9" s="28" t="s">
+        <v>53</v>
+      </c>
+      <c r="U9" s="28" t="s">
         <v>178</v>
       </c>
-      <c r="M9" s="18" t="s">
-        <v>48</v>
-      </c>
-      <c r="N9" s="18" t="s">
-        <v>49</v>
-      </c>
-      <c r="O9" s="19" t="s">
+      <c r="V9" s="28" t="s">
+        <v>54</v>
+      </c>
+      <c r="W9" s="28" t="s">
+        <v>55</v>
+      </c>
+      <c r="X9" s="28" t="s">
         <v>179</v>
       </c>
-      <c r="P9" s="18" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q9" s="18" t="s">
-        <v>51</v>
-      </c>
-      <c r="R9" s="19" t="s">
+      <c r="Y9" s="28" t="s">
+        <v>56</v>
+      </c>
+      <c r="Z9" s="28" t="s">
+        <v>57</v>
+      </c>
+      <c r="AA9" s="28" t="s">
         <v>180</v>
       </c>
-      <c r="S9" s="18" t="s">
-        <v>52</v>
-      </c>
-      <c r="T9" s="18" t="s">
-        <v>53</v>
-      </c>
-      <c r="U9" s="19" t="s">
+      <c r="AB9" s="28" t="s">
+        <v>58</v>
+      </c>
+      <c r="AC9" s="28" t="s">
+        <v>59</v>
+      </c>
+      <c r="AD9" s="28" t="s">
         <v>181</v>
       </c>
-      <c r="V9" s="18" t="s">
-        <v>54</v>
-      </c>
-      <c r="W9" s="18" t="s">
-        <v>55</v>
-      </c>
-      <c r="X9" s="19" t="s">
+      <c r="AE9" s="28" t="s">
+        <v>60</v>
+      </c>
+      <c r="AF9" s="28" t="s">
+        <v>61</v>
+      </c>
+      <c r="AG9" s="28" t="s">
         <v>182</v>
       </c>
-      <c r="Y9" s="18" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z9" s="18" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA9" s="19" t="s">
+      <c r="AH9" s="28" t="s">
+        <v>62</v>
+      </c>
+      <c r="AI9" s="28" t="s">
+        <v>63</v>
+      </c>
+      <c r="AJ9" s="28" t="s">
+        <v>64</v>
+      </c>
+      <c r="AK9" s="28" t="s">
+        <v>165</v>
+      </c>
+      <c r="AL9" s="28" t="s">
+        <v>65</v>
+      </c>
+      <c r="AM9" s="28" t="s">
+        <v>66</v>
+      </c>
+      <c r="AN9" s="28" t="s">
+        <v>67</v>
+      </c>
+      <c r="AO9" s="28" t="s">
+        <v>166</v>
+      </c>
+      <c r="AP9" s="28" t="s">
+        <v>68</v>
+      </c>
+      <c r="AQ9" s="28" t="s">
+        <v>69</v>
+      </c>
+      <c r="AR9" s="28" t="s">
+        <v>70</v>
+      </c>
+      <c r="AS9" s="28" t="s">
+        <v>167</v>
+      </c>
+      <c r="AT9" s="28" t="s">
+        <v>71</v>
+      </c>
+      <c r="AU9" s="28" t="s">
+        <v>72</v>
+      </c>
+      <c r="AV9" s="28" t="s">
+        <v>73</v>
+      </c>
+      <c r="AW9" s="28" t="s">
+        <v>168</v>
+      </c>
+      <c r="AX9" s="28" t="s">
+        <v>74</v>
+      </c>
+      <c r="AY9" s="28" t="s">
+        <v>75</v>
+      </c>
+      <c r="AZ9" s="28" t="s">
+        <v>76</v>
+      </c>
+      <c r="BA9" s="28" t="s">
+        <v>169</v>
+      </c>
+      <c r="BB9" s="28" t="s">
+        <v>77</v>
+      </c>
+      <c r="BC9" s="28" t="s">
+        <v>78</v>
+      </c>
+      <c r="BD9" s="28" t="s">
+        <v>79</v>
+      </c>
+      <c r="BE9" s="28" t="s">
+        <v>80</v>
+      </c>
+      <c r="BF9" s="28" t="s">
+        <v>81</v>
+      </c>
+      <c r="BG9" s="28" t="s">
+        <v>170</v>
+      </c>
+      <c r="BH9" s="28" t="s">
+        <v>82</v>
+      </c>
+      <c r="BI9" s="28" t="s">
+        <v>83</v>
+      </c>
+      <c r="BJ9" s="28" t="s">
+        <v>84</v>
+      </c>
+      <c r="BK9" s="28" t="s">
+        <v>171</v>
+      </c>
+      <c r="BL9" s="28" t="s">
+        <v>85</v>
+      </c>
+      <c r="BM9" s="28" t="s">
+        <v>86</v>
+      </c>
+      <c r="BN9" s="28" t="s">
+        <v>87</v>
+      </c>
+      <c r="BO9" s="28" t="s">
+        <v>172</v>
+      </c>
+      <c r="BP9" s="28" t="s">
         <v>183</v>
       </c>
-      <c r="AB9" s="18" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC9" s="18" t="s">
-        <v>59</v>
-      </c>
-      <c r="AD9" s="19" t="s">
+      <c r="BQ9" s="28" t="s">
         <v>184</v>
       </c>
-      <c r="AE9" s="18" t="s">
-        <v>60</v>
-      </c>
-      <c r="AF9" s="18" t="s">
-        <v>61</v>
-      </c>
-      <c r="AG9" s="19" t="s">
+      <c r="BR9" s="28" t="s">
         <v>185</v>
       </c>
-      <c r="AH9" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="AI9" s="18" t="s">
-        <v>63</v>
-      </c>
-      <c r="AJ9" s="18" t="s">
-        <v>64</v>
-      </c>
-      <c r="AK9" s="19" t="s">
-        <v>165</v>
-      </c>
-      <c r="AL9" s="18" t="s">
-        <v>65</v>
-      </c>
-      <c r="AM9" s="18" t="s">
-        <v>66</v>
-      </c>
-      <c r="AN9" s="18" t="s">
-        <v>67</v>
-      </c>
-      <c r="AO9" s="19" t="s">
-        <v>166</v>
-      </c>
-      <c r="AP9" s="18" t="s">
-        <v>68</v>
-      </c>
-      <c r="AQ9" s="18" t="s">
-        <v>69</v>
-      </c>
-      <c r="AR9" s="18" t="s">
-        <v>70</v>
-      </c>
-      <c r="AS9" s="19" t="s">
-        <v>167</v>
-      </c>
-      <c r="AT9" s="18" t="s">
-        <v>71</v>
-      </c>
-      <c r="AU9" s="18" t="s">
-        <v>72</v>
-      </c>
-      <c r="AV9" s="18" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW9" s="19" t="s">
-        <v>168</v>
-      </c>
-      <c r="AX9" s="18" t="s">
-        <v>74</v>
-      </c>
-      <c r="AY9" s="18" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ9" s="18" t="s">
-        <v>76</v>
-      </c>
-      <c r="BA9" s="19" t="s">
-        <v>169</v>
-      </c>
-      <c r="BB9" s="18" t="s">
-        <v>77</v>
-      </c>
-      <c r="BC9" s="18" t="s">
-        <v>78</v>
-      </c>
-      <c r="BD9" s="18" t="s">
-        <v>79</v>
-      </c>
-      <c r="BE9" s="18" t="s">
-        <v>80</v>
-      </c>
-      <c r="BF9" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="BG9" s="19" t="s">
-        <v>170</v>
-      </c>
-      <c r="BH9" s="18" t="s">
-        <v>82</v>
-      </c>
-      <c r="BI9" s="18" t="s">
-        <v>83</v>
-      </c>
-      <c r="BJ9" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="BK9" s="19" t="s">
-        <v>171</v>
-      </c>
-      <c r="BL9" s="18" t="s">
-        <v>85</v>
-      </c>
-      <c r="BM9" s="18" t="s">
-        <v>86</v>
-      </c>
-      <c r="BN9" s="18" t="s">
-        <v>87</v>
-      </c>
-      <c r="BO9" s="19" t="s">
-        <v>172</v>
-      </c>
-      <c r="BP9" s="18" t="s">
+      <c r="BS9" s="28" t="s">
         <v>173</v>
       </c>
-      <c r="BQ9" s="18" t="s">
-        <v>174</v>
-      </c>
-      <c r="BR9" s="18" t="s">
-        <v>175</v>
-      </c>
-      <c r="BS9" s="19" t="s">
-        <v>176</v>
-      </c>
-      <c r="BT9" s="18" t="s">
+      <c r="BT9" s="28" t="s">
         <v>88</v>
       </c>
-      <c r="BU9" s="20" t="s">
+      <c r="BU9" s="29" t="s">
         <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:73" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A10" s="21" t="s">
+      <c r="A10" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="B10" s="21" t="s">
+      <c r="B10" s="18" t="s">
         <v>92</v>
       </c>
-      <c r="C10" s="22" t="s">
+      <c r="C10" s="30" t="s">
         <v>93</v>
       </c>
-      <c r="D10" s="22" t="s">
+      <c r="D10" s="30" t="s">
         <v>94</v>
       </c>
-      <c r="E10" s="22" t="s">
+      <c r="E10" s="30" t="s">
         <v>95</v>
       </c>
-      <c r="F10" s="23" t="s">
+      <c r="F10" s="30" t="s">
         <v>96</v>
       </c>
-      <c r="G10" s="22" t="s">
+      <c r="G10" s="30" t="s">
         <v>97</v>
       </c>
-      <c r="H10" s="22" t="s">
+      <c r="H10" s="30" t="s">
         <v>98</v>
       </c>
-      <c r="I10" s="23" t="s">
+      <c r="I10" s="30" t="s">
         <v>99</v>
       </c>
-      <c r="J10" s="22" t="s">
+      <c r="J10" s="30" t="s">
         <v>100</v>
       </c>
-      <c r="K10" s="22" t="s">
+      <c r="K10" s="30" t="s">
         <v>101</v>
       </c>
-      <c r="L10" s="23" t="s">
+      <c r="L10" s="30" t="s">
         <v>102</v>
       </c>
-      <c r="M10" s="22" t="s">
+      <c r="M10" s="30" t="s">
         <v>103</v>
       </c>
-      <c r="N10" s="22" t="s">
+      <c r="N10" s="30" t="s">
         <v>104</v>
       </c>
-      <c r="O10" s="23" t="s">
+      <c r="O10" s="30" t="s">
         <v>105</v>
       </c>
-      <c r="P10" s="22" t="s">
+      <c r="P10" s="30" t="s">
         <v>106</v>
       </c>
-      <c r="Q10" s="22" t="s">
+      <c r="Q10" s="30" t="s">
         <v>107</v>
       </c>
-      <c r="R10" s="23" t="s">
+      <c r="R10" s="30" t="s">
         <v>108</v>
       </c>
-      <c r="S10" s="22" t="s">
+      <c r="S10" s="30" t="s">
         <v>109</v>
       </c>
-      <c r="T10" s="22" t="s">
+      <c r="T10" s="30" t="s">
         <v>110</v>
       </c>
-      <c r="U10" s="23" t="s">
+      <c r="U10" s="30" t="s">
         <v>111</v>
       </c>
-      <c r="V10" s="22" t="s">
+      <c r="V10" s="30" t="s">
         <v>112</v>
       </c>
-      <c r="W10" s="22" t="s">
+      <c r="W10" s="30" t="s">
         <v>113</v>
       </c>
-      <c r="X10" s="23" t="s">
+      <c r="X10" s="30" t="s">
         <v>114</v>
       </c>
-      <c r="Y10" s="22" t="s">
+      <c r="Y10" s="30" t="s">
         <v>115</v>
       </c>
-      <c r="Z10" s="22" t="s">
+      <c r="Z10" s="30" t="s">
         <v>116</v>
       </c>
-      <c r="AA10" s="23" t="s">
+      <c r="AA10" s="30" t="s">
         <v>117</v>
       </c>
-      <c r="AB10" s="22" t="s">
+      <c r="AB10" s="30" t="s">
         <v>118</v>
       </c>
-      <c r="AC10" s="22" t="s">
+      <c r="AC10" s="30" t="s">
         <v>119</v>
       </c>
-      <c r="AD10" s="23" t="s">
+      <c r="AD10" s="30" t="s">
         <v>120</v>
       </c>
-      <c r="AE10" s="22" t="s">
+      <c r="AE10" s="30" t="s">
         <v>121</v>
       </c>
-      <c r="AF10" s="22" t="s">
+      <c r="AF10" s="30" t="s">
         <v>122</v>
       </c>
-      <c r="AG10" s="23" t="s">
+      <c r="AG10" s="30" t="s">
         <v>123</v>
       </c>
-      <c r="AH10" s="22" t="s">
+      <c r="AH10" s="30" t="s">
         <v>124</v>
       </c>
-      <c r="AI10" s="22" t="s">
+      <c r="AI10" s="30" t="s">
         <v>125</v>
       </c>
-      <c r="AJ10" s="22" t="s">
+      <c r="AJ10" s="30" t="s">
         <v>126</v>
       </c>
-      <c r="AK10" s="23" t="s">
+      <c r="AK10" s="30" t="s">
         <v>127</v>
       </c>
-      <c r="AL10" s="22" t="s">
+      <c r="AL10" s="30" t="s">
         <v>128</v>
       </c>
-      <c r="AM10" s="22" t="s">
+      <c r="AM10" s="30" t="s">
         <v>129</v>
       </c>
-      <c r="AN10" s="22" t="s">
+      <c r="AN10" s="30" t="s">
         <v>130</v>
       </c>
-      <c r="AO10" s="23" t="s">
+      <c r="AO10" s="30" t="s">
         <v>131</v>
       </c>
-      <c r="AP10" s="24" t="s">
+      <c r="AP10" s="31" t="s">
         <v>132</v>
       </c>
-      <c r="AQ10" s="24" t="s">
+      <c r="AQ10" s="31" t="s">
         <v>133</v>
       </c>
-      <c r="AR10" s="24" t="s">
+      <c r="AR10" s="31" t="s">
         <v>134</v>
       </c>
-      <c r="AS10" s="23" t="s">
+      <c r="AS10" s="30" t="s">
         <v>135</v>
       </c>
-      <c r="AT10" s="22" t="s">
+      <c r="AT10" s="30" t="s">
         <v>136</v>
       </c>
-      <c r="AU10" s="22" t="s">
+      <c r="AU10" s="30" t="s">
         <v>137</v>
       </c>
-      <c r="AV10" s="22" t="s">
+      <c r="AV10" s="30" t="s">
         <v>138</v>
       </c>
-      <c r="AW10" s="23" t="s">
+      <c r="AW10" s="30" t="s">
         <v>139</v>
       </c>
-      <c r="AX10" s="22" t="s">
+      <c r="AX10" s="30" t="s">
         <v>140</v>
       </c>
-      <c r="AY10" s="22" t="s">
+      <c r="AY10" s="30" t="s">
         <v>141</v>
       </c>
-      <c r="AZ10" s="22" t="s">
+      <c r="AZ10" s="30" t="s">
         <v>142</v>
       </c>
-      <c r="BA10" s="23" t="s">
+      <c r="BA10" s="30" t="s">
         <v>143</v>
       </c>
-      <c r="BB10" s="22" t="s">
+      <c r="BB10" s="30" t="s">
         <v>144</v>
       </c>
-      <c r="BC10" s="22" t="s">
+      <c r="BC10" s="30" t="s">
         <v>145</v>
       </c>
-      <c r="BD10" s="22" t="s">
+      <c r="BD10" s="30" t="s">
         <v>146</v>
       </c>
-      <c r="BE10" s="22" t="s">
+      <c r="BE10" s="30" t="s">
         <v>147</v>
       </c>
-      <c r="BF10" s="22" t="s">
+      <c r="BF10" s="30" t="s">
         <v>148</v>
       </c>
-      <c r="BG10" s="23" t="s">
+      <c r="BG10" s="30" t="s">
         <v>149</v>
       </c>
-      <c r="BH10" s="22" t="s">
+      <c r="BH10" s="30" t="s">
         <v>150</v>
       </c>
-      <c r="BI10" s="22" t="s">
+      <c r="BI10" s="30" t="s">
         <v>151</v>
       </c>
-      <c r="BJ10" s="22" t="s">
+      <c r="BJ10" s="30" t="s">
         <v>152</v>
       </c>
-      <c r="BK10" s="23" t="s">
+      <c r="BK10" s="30" t="s">
         <v>153</v>
       </c>
-      <c r="BL10" s="22" t="s">
+      <c r="BL10" s="30" t="s">
         <v>154</v>
       </c>
-      <c r="BM10" s="22" t="s">
+      <c r="BM10" s="30" t="s">
         <v>155</v>
       </c>
-      <c r="BN10" s="22" t="s">
+      <c r="BN10" s="30" t="s">
         <v>156</v>
       </c>
-      <c r="BO10" s="23" t="s">
+      <c r="BO10" s="30" t="s">
         <v>157</v>
       </c>
-      <c r="BP10" s="22" t="s">
+      <c r="BP10" s="30" t="s">
         <v>158</v>
       </c>
-      <c r="BQ10" s="22" t="s">
+      <c r="BQ10" s="30" t="s">
         <v>159</v>
       </c>
-      <c r="BR10" s="22" t="s">
+      <c r="BR10" s="30" t="s">
         <v>160</v>
       </c>
-      <c r="BS10" s="23" t="s">
+      <c r="BS10" s="30" t="s">
         <v>161</v>
       </c>
-      <c r="BT10" s="22" t="s">
+      <c r="BT10" s="30" t="s">
         <v>162</v>
       </c>
-      <c r="BU10" s="22" t="s">
+      <c r="BU10" s="30" t="s">
         <v>163</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="AB5:AD7"/>
-    <mergeCell ref="AE5:AG7"/>
-    <mergeCell ref="AH5:BK5"/>
-    <mergeCell ref="BL5:BS5"/>
-    <mergeCell ref="BT5:BT6"/>
-    <mergeCell ref="BU5:BU6"/>
-    <mergeCell ref="AH6:AK6"/>
-    <mergeCell ref="AL6:AO6"/>
-    <mergeCell ref="AP6:AS6"/>
-    <mergeCell ref="AT6:AW6"/>
-    <mergeCell ref="BP6:BS6"/>
-    <mergeCell ref="AX6:BA6"/>
-    <mergeCell ref="BB6:BB7"/>
-    <mergeCell ref="BC6:BC7"/>
-    <mergeCell ref="BD6:BG6"/>
-    <mergeCell ref="BH6:BK6"/>
-    <mergeCell ref="BL6:BO6"/>
     <mergeCell ref="C1:L1"/>
     <mergeCell ref="C2:K2"/>
     <mergeCell ref="A5:A8"/>
@@ -2304,6 +2284,23 @@
     <mergeCell ref="S7:U7"/>
     <mergeCell ref="V7:X7"/>
     <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="BU5:BU6"/>
+    <mergeCell ref="AH6:AK6"/>
+    <mergeCell ref="AL6:AO6"/>
+    <mergeCell ref="AP6:AS6"/>
+    <mergeCell ref="AT6:AW6"/>
+    <mergeCell ref="BP6:BS6"/>
+    <mergeCell ref="AX6:BA6"/>
+    <mergeCell ref="BB6:BB7"/>
+    <mergeCell ref="BC6:BC7"/>
+    <mergeCell ref="BD6:BG6"/>
+    <mergeCell ref="BH6:BK6"/>
+    <mergeCell ref="BL6:BO6"/>
+    <mergeCell ref="AB5:AD7"/>
+    <mergeCell ref="AE5:AG7"/>
+    <mergeCell ref="AH5:BK5"/>
+    <mergeCell ref="BL5:BS5"/>
+    <mergeCell ref="BT5:BT6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/src/main/resources/templates/summaryReportForm2.xlsx
+++ b/src/main/resources/templates/summaryReportForm2.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21231"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C884BDB4-FEA3-4A43-AF6C-3E6D79A24E33}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE792F9-5280-4943-A42A-445A2DD3BD40}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="189">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="281" uniqueCount="188">
   <si>
     <t>Оперативная информация</t>
   </si>
@@ -98,9 +98,6 @@
   </si>
   <si>
     <t>на 1 усл.гол.заготовлено цент.к.ед.</t>
-  </si>
-  <si>
-    <t>факт прошл.года</t>
   </si>
   <si>
     <t>план</t>
@@ -817,44 +814,44 @@
     <xf numFmtId="49" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="6" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
-    </xf>
-    <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1140,24 +1137,26 @@
   <dimension ref="A1:BU10"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="42.7109375" customWidth="1"/>
-    <col min="2" max="2" width="12.7109375" customWidth="1"/>
-    <col min="3" max="73" width="10.7109375" customWidth="1"/>
+    <col min="1" max="1" width="45.7109375" customWidth="1"/>
+    <col min="2" max="2" width="15.7109375" customWidth="1"/>
+    <col min="3" max="53" width="10.7109375" customWidth="1"/>
+    <col min="54" max="54" width="11.28515625" customWidth="1"/>
+    <col min="55" max="73" width="10.7109375" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="C1" s="24" t="s">
+      <c r="C1" s="23" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="24"/>
-      <c r="E1" s="24"/>
-      <c r="F1" s="24"/>
-      <c r="G1" s="24"/>
-      <c r="H1" s="24"/>
-      <c r="I1" s="24"/>
-      <c r="J1" s="24"/>
-      <c r="K1" s="24"/>
-      <c r="L1" s="24"/>
+      <c r="D1" s="23"/>
+      <c r="E1" s="23"/>
+      <c r="F1" s="23"/>
+      <c r="G1" s="23"/>
+      <c r="H1" s="23"/>
+      <c r="I1" s="23"/>
+      <c r="J1" s="23"/>
+      <c r="K1" s="23"/>
+      <c r="L1" s="23"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
@@ -1199,17 +1198,17 @@
       <c r="AY1" s="1"/>
     </row>
     <row r="2" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="C2" s="24" t="s">
+      <c r="C2" s="23" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="24"/>
-      <c r="E2" s="24"/>
-      <c r="F2" s="24"/>
-      <c r="G2" s="24"/>
-      <c r="H2" s="24"/>
-      <c r="I2" s="24"/>
-      <c r="J2" s="24"/>
-      <c r="K2" s="24"/>
+      <c r="D2" s="23"/>
+      <c r="E2" s="23"/>
+      <c r="F2" s="23"/>
+      <c r="G2" s="23"/>
+      <c r="H2" s="23"/>
+      <c r="I2" s="23"/>
+      <c r="J2" s="23"/>
+      <c r="K2" s="23"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
@@ -1257,14 +1256,14 @@
         <v>2</v>
       </c>
       <c r="H3" s="3" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
     </row>
     <row r="5" spans="1:73" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="23" t="s">
+      <c r="A5" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="23" t="s">
+      <c r="B5" s="24" t="s">
         <v>4</v>
       </c>
       <c r="C5" s="26" t="s">
@@ -1273,1002 +1272,1019 @@
       <c r="D5" s="26"/>
       <c r="E5" s="26"/>
       <c r="F5" s="26"/>
-      <c r="G5" s="20" t="s">
+      <c r="G5" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="20"/>
-      <c r="I5" s="20"/>
-      <c r="J5" s="20"/>
-      <c r="K5" s="20"/>
-      <c r="L5" s="20"/>
-      <c r="M5" s="20"/>
-      <c r="N5" s="20"/>
-      <c r="O5" s="20"/>
-      <c r="P5" s="20"/>
-      <c r="Q5" s="20"/>
-      <c r="R5" s="20"/>
-      <c r="S5" s="20"/>
-      <c r="T5" s="20"/>
-      <c r="U5" s="20"/>
-      <c r="V5" s="20"/>
-      <c r="W5" s="20"/>
-      <c r="X5" s="20"/>
-      <c r="Y5" s="20"/>
-      <c r="Z5" s="20"/>
-      <c r="AA5" s="20"/>
-      <c r="AB5" s="19" t="s">
+      <c r="H5" s="27"/>
+      <c r="I5" s="27"/>
+      <c r="J5" s="27"/>
+      <c r="K5" s="27"/>
+      <c r="L5" s="27"/>
+      <c r="M5" s="27"/>
+      <c r="N5" s="27"/>
+      <c r="O5" s="27"/>
+      <c r="P5" s="27"/>
+      <c r="Q5" s="27"/>
+      <c r="R5" s="27"/>
+      <c r="S5" s="27"/>
+      <c r="T5" s="27"/>
+      <c r="U5" s="27"/>
+      <c r="V5" s="27"/>
+      <c r="W5" s="27"/>
+      <c r="X5" s="27"/>
+      <c r="Y5" s="27"/>
+      <c r="Z5" s="27"/>
+      <c r="AA5" s="27"/>
+      <c r="AB5" s="31" t="s">
         <v>7</v>
       </c>
-      <c r="AC5" s="19"/>
-      <c r="AD5" s="19"/>
-      <c r="AE5" s="20" t="s">
+      <c r="AC5" s="31"/>
+      <c r="AD5" s="31"/>
+      <c r="AE5" s="27" t="s">
         <v>8</v>
       </c>
-      <c r="AF5" s="20"/>
-      <c r="AG5" s="20"/>
-      <c r="AH5" s="21" t="s">
+      <c r="AF5" s="27"/>
+      <c r="AG5" s="27"/>
+      <c r="AH5" s="30" t="s">
         <v>9</v>
       </c>
-      <c r="AI5" s="21"/>
-      <c r="AJ5" s="21"/>
-      <c r="AK5" s="21"/>
-      <c r="AL5" s="21"/>
-      <c r="AM5" s="21"/>
-      <c r="AN5" s="21"/>
-      <c r="AO5" s="21"/>
-      <c r="AP5" s="21"/>
-      <c r="AQ5" s="21"/>
-      <c r="AR5" s="21"/>
-      <c r="AS5" s="21"/>
-      <c r="AT5" s="21"/>
-      <c r="AU5" s="21"/>
-      <c r="AV5" s="21"/>
-      <c r="AW5" s="21"/>
-      <c r="AX5" s="21"/>
-      <c r="AY5" s="21"/>
-      <c r="AZ5" s="21"/>
-      <c r="BA5" s="21"/>
-      <c r="BB5" s="21"/>
-      <c r="BC5" s="21"/>
-      <c r="BD5" s="21"/>
-      <c r="BE5" s="21"/>
-      <c r="BF5" s="21"/>
-      <c r="BG5" s="21"/>
-      <c r="BH5" s="21"/>
-      <c r="BI5" s="21"/>
-      <c r="BJ5" s="21"/>
-      <c r="BK5" s="21"/>
-      <c r="BL5" s="21" t="s">
+      <c r="AI5" s="30"/>
+      <c r="AJ5" s="30"/>
+      <c r="AK5" s="30"/>
+      <c r="AL5" s="30"/>
+      <c r="AM5" s="30"/>
+      <c r="AN5" s="30"/>
+      <c r="AO5" s="30"/>
+      <c r="AP5" s="30"/>
+      <c r="AQ5" s="30"/>
+      <c r="AR5" s="30"/>
+      <c r="AS5" s="30"/>
+      <c r="AT5" s="30"/>
+      <c r="AU5" s="30"/>
+      <c r="AV5" s="30"/>
+      <c r="AW5" s="30"/>
+      <c r="AX5" s="30"/>
+      <c r="AY5" s="30"/>
+      <c r="AZ5" s="30"/>
+      <c r="BA5" s="30"/>
+      <c r="BB5" s="30"/>
+      <c r="BC5" s="30"/>
+      <c r="BD5" s="30"/>
+      <c r="BE5" s="30"/>
+      <c r="BF5" s="30"/>
+      <c r="BG5" s="30"/>
+      <c r="BH5" s="30"/>
+      <c r="BI5" s="30"/>
+      <c r="BJ5" s="30"/>
+      <c r="BK5" s="30"/>
+      <c r="BL5" s="30" t="s">
         <v>10</v>
       </c>
-      <c r="BM5" s="21"/>
-      <c r="BN5" s="21"/>
-      <c r="BO5" s="21"/>
-      <c r="BP5" s="21"/>
-      <c r="BQ5" s="21"/>
-      <c r="BR5" s="21"/>
-      <c r="BS5" s="21"/>
-      <c r="BT5" s="22" t="s">
+      <c r="BM5" s="30"/>
+      <c r="BN5" s="30"/>
+      <c r="BO5" s="30"/>
+      <c r="BP5" s="30"/>
+      <c r="BQ5" s="30"/>
+      <c r="BR5" s="30"/>
+      <c r="BS5" s="30"/>
+      <c r="BT5" s="29" t="s">
         <v>11</v>
       </c>
-      <c r="BU5" s="22" t="s">
+      <c r="BU5" s="29" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:73" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="23"/>
-      <c r="B6" s="23"/>
+      <c r="A6" s="24"/>
+      <c r="B6" s="24"/>
       <c r="C6" s="26"/>
       <c r="D6" s="26"/>
       <c r="E6" s="26"/>
       <c r="F6" s="26"/>
-      <c r="G6" s="20" t="s">
+      <c r="G6" s="27" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="20"/>
-      <c r="I6" s="20"/>
-      <c r="J6" s="20"/>
-      <c r="K6" s="20"/>
-      <c r="L6" s="20"/>
-      <c r="M6" s="20"/>
-      <c r="N6" s="20"/>
-      <c r="O6" s="20"/>
-      <c r="P6" s="20"/>
-      <c r="Q6" s="20"/>
-      <c r="R6" s="20"/>
-      <c r="S6" s="20" t="s">
+      <c r="H6" s="27"/>
+      <c r="I6" s="27"/>
+      <c r="J6" s="27"/>
+      <c r="K6" s="27"/>
+      <c r="L6" s="27"/>
+      <c r="M6" s="27"/>
+      <c r="N6" s="27"/>
+      <c r="O6" s="27"/>
+      <c r="P6" s="27"/>
+      <c r="Q6" s="27"/>
+      <c r="R6" s="27"/>
+      <c r="S6" s="27" t="s">
         <v>14</v>
       </c>
-      <c r="T6" s="20"/>
-      <c r="U6" s="20"/>
-      <c r="V6" s="20"/>
-      <c r="W6" s="20"/>
-      <c r="X6" s="20"/>
-      <c r="Y6" s="20"/>
-      <c r="Z6" s="20"/>
-      <c r="AA6" s="20"/>
-      <c r="AB6" s="19"/>
-      <c r="AC6" s="19"/>
-      <c r="AD6" s="19"/>
-      <c r="AE6" s="20"/>
-      <c r="AF6" s="20"/>
-      <c r="AG6" s="20"/>
-      <c r="AH6" s="21" t="s">
+      <c r="T6" s="27"/>
+      <c r="U6" s="27"/>
+      <c r="V6" s="27"/>
+      <c r="W6" s="27"/>
+      <c r="X6" s="27"/>
+      <c r="Y6" s="27"/>
+      <c r="Z6" s="27"/>
+      <c r="AA6" s="27"/>
+      <c r="AB6" s="31"/>
+      <c r="AC6" s="31"/>
+      <c r="AD6" s="31"/>
+      <c r="AE6" s="27"/>
+      <c r="AF6" s="27"/>
+      <c r="AG6" s="27"/>
+      <c r="AH6" s="30" t="s">
         <v>15</v>
       </c>
-      <c r="AI6" s="21"/>
-      <c r="AJ6" s="21"/>
-      <c r="AK6" s="21"/>
-      <c r="AL6" s="21" t="s">
+      <c r="AI6" s="30"/>
+      <c r="AJ6" s="30"/>
+      <c r="AK6" s="30"/>
+      <c r="AL6" s="30" t="s">
         <v>16</v>
       </c>
-      <c r="AM6" s="21"/>
-      <c r="AN6" s="21"/>
-      <c r="AO6" s="21"/>
-      <c r="AP6" s="21" t="s">
+      <c r="AM6" s="30"/>
+      <c r="AN6" s="30"/>
+      <c r="AO6" s="30"/>
+      <c r="AP6" s="30" t="s">
         <v>17</v>
       </c>
-      <c r="AQ6" s="21"/>
-      <c r="AR6" s="21"/>
-      <c r="AS6" s="21"/>
-      <c r="AT6" s="21" t="s">
+      <c r="AQ6" s="30"/>
+      <c r="AR6" s="30"/>
+      <c r="AS6" s="30"/>
+      <c r="AT6" s="30" t="s">
         <v>18</v>
       </c>
-      <c r="AU6" s="21"/>
-      <c r="AV6" s="21"/>
-      <c r="AW6" s="21"/>
-      <c r="AX6" s="21" t="s">
+      <c r="AU6" s="30"/>
+      <c r="AV6" s="30"/>
+      <c r="AW6" s="30"/>
+      <c r="AX6" s="30" t="s">
         <v>19</v>
       </c>
-      <c r="AY6" s="21"/>
-      <c r="AZ6" s="21"/>
-      <c r="BA6" s="21"/>
-      <c r="BB6" s="23" t="s">
+      <c r="AY6" s="30"/>
+      <c r="AZ6" s="30"/>
+      <c r="BA6" s="30"/>
+      <c r="BB6" s="24" t="s">
         <v>20</v>
       </c>
-      <c r="BC6" s="23" t="s">
+      <c r="BC6" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="BD6" s="21" t="s">
+      <c r="BD6" s="30" t="s">
         <v>22</v>
       </c>
-      <c r="BE6" s="21"/>
-      <c r="BF6" s="21"/>
-      <c r="BG6" s="21"/>
-      <c r="BH6" s="21" t="s">
+      <c r="BE6" s="30"/>
+      <c r="BF6" s="30"/>
+      <c r="BG6" s="30"/>
+      <c r="BH6" s="30" t="s">
         <v>23</v>
       </c>
-      <c r="BI6" s="21"/>
-      <c r="BJ6" s="21"/>
-      <c r="BK6" s="21"/>
-      <c r="BL6" s="21" t="s">
+      <c r="BI6" s="30"/>
+      <c r="BJ6" s="30"/>
+      <c r="BK6" s="30"/>
+      <c r="BL6" s="30" t="s">
         <v>24</v>
       </c>
-      <c r="BM6" s="21"/>
-      <c r="BN6" s="21"/>
-      <c r="BO6" s="21"/>
-      <c r="BP6" s="21" t="s">
+      <c r="BM6" s="30"/>
+      <c r="BN6" s="30"/>
+      <c r="BO6" s="30"/>
+      <c r="BP6" s="30" t="s">
         <v>25</v>
       </c>
-      <c r="BQ6" s="21"/>
-      <c r="BR6" s="21"/>
-      <c r="BS6" s="21"/>
-      <c r="BT6" s="22"/>
-      <c r="BU6" s="22"/>
+      <c r="BQ6" s="30"/>
+      <c r="BR6" s="30"/>
+      <c r="BS6" s="30"/>
+      <c r="BT6" s="29"/>
+      <c r="BU6" s="29"/>
     </row>
     <row r="7" spans="1:73" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="23"/>
-      <c r="B7" s="23"/>
+      <c r="A7" s="24"/>
+      <c r="B7" s="24"/>
       <c r="C7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="D7" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="D7" s="7" t="s">
+      <c r="E7" s="7" t="s">
         <v>27</v>
       </c>
-      <c r="E7" s="7" t="s">
+      <c r="F7" s="8"/>
+      <c r="G7" s="28" t="s">
         <v>28</v>
       </c>
-      <c r="F7" s="8"/>
-      <c r="G7" s="27" t="s">
+      <c r="H7" s="28"/>
+      <c r="I7" s="28"/>
+      <c r="J7" s="28" t="s">
         <v>29</v>
       </c>
-      <c r="H7" s="27"/>
-      <c r="I7" s="27"/>
-      <c r="J7" s="27" t="s">
+      <c r="K7" s="28"/>
+      <c r="L7" s="28"/>
+      <c r="M7" s="28" t="s">
         <v>30</v>
       </c>
-      <c r="K7" s="27"/>
-      <c r="L7" s="27"/>
-      <c r="M7" s="27" t="s">
+      <c r="N7" s="28"/>
+      <c r="O7" s="28"/>
+      <c r="P7" s="28" t="s">
         <v>31</v>
       </c>
-      <c r="N7" s="27"/>
-      <c r="O7" s="27"/>
-      <c r="P7" s="27" t="s">
+      <c r="Q7" s="28"/>
+      <c r="R7" s="28"/>
+      <c r="S7" s="28" t="s">
+        <v>28</v>
+      </c>
+      <c r="T7" s="28"/>
+      <c r="U7" s="28"/>
+      <c r="V7" s="28" t="s">
+        <v>29</v>
+      </c>
+      <c r="W7" s="28"/>
+      <c r="X7" s="28"/>
+      <c r="Y7" s="28" t="s">
         <v>32</v>
       </c>
-      <c r="Q7" s="27"/>
-      <c r="R7" s="27"/>
-      <c r="S7" s="27" t="s">
-        <v>29</v>
-      </c>
-      <c r="T7" s="27"/>
-      <c r="U7" s="27"/>
-      <c r="V7" s="27" t="s">
-        <v>30</v>
-      </c>
-      <c r="W7" s="27"/>
-      <c r="X7" s="27"/>
-      <c r="Y7" s="27" t="s">
+      <c r="Z7" s="28"/>
+      <c r="AA7" s="28"/>
+      <c r="AB7" s="31"/>
+      <c r="AC7" s="31"/>
+      <c r="AD7" s="31"/>
+      <c r="AE7" s="27"/>
+      <c r="AF7" s="27"/>
+      <c r="AG7" s="27"/>
+      <c r="AH7" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="Z7" s="27"/>
-      <c r="AA7" s="27"/>
-      <c r="AB7" s="19"/>
-      <c r="AC7" s="19"/>
-      <c r="AD7" s="19"/>
-      <c r="AE7" s="20"/>
-      <c r="AF7" s="20"/>
-      <c r="AG7" s="20"/>
-      <c r="AH7" s="7" t="s">
+      <c r="AI7" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AI7" s="7" t="s">
+      <c r="AJ7" s="7" t="s">
         <v>27</v>
-      </c>
-      <c r="AJ7" s="7" t="s">
-        <v>28</v>
       </c>
       <c r="AK7" s="8"/>
       <c r="AL7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="AM7" s="7" t="s">
         <v>26</v>
       </c>
-      <c r="AM7" s="7" t="s">
+      <c r="AN7" s="7" t="s">
         <v>27</v>
-      </c>
-      <c r="AN7" s="7" t="s">
-        <v>28</v>
       </c>
       <c r="AO7" s="8"/>
       <c r="AP7" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AQ7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="AR7" s="7" t="s">
         <v>27</v>
-      </c>
-      <c r="AR7" s="7" t="s">
-        <v>28</v>
       </c>
       <c r="AS7" s="8"/>
       <c r="AT7" s="7" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="AU7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="AV7" s="7" t="s">
         <v>27</v>
-      </c>
-      <c r="AV7" s="7" t="s">
-        <v>28</v>
       </c>
       <c r="AW7" s="8"/>
       <c r="AX7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="AY7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="AZ7" s="7" t="s">
+        <v>27</v>
+      </c>
+      <c r="BA7" s="9"/>
+      <c r="BB7" s="24"/>
+      <c r="BC7" s="24"/>
+      <c r="BD7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="BE7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="BF7" s="7" t="s">
         <v>34</v>
-      </c>
-      <c r="AY7" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="AZ7" s="7" t="s">
-        <v>28</v>
-      </c>
-      <c r="BA7" s="9"/>
-      <c r="BB7" s="23"/>
-      <c r="BC7" s="23"/>
-      <c r="BD7" s="7" t="s">
-        <v>34</v>
-      </c>
-      <c r="BE7" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="BF7" s="7" t="s">
-        <v>35</v>
       </c>
       <c r="BG7" s="10"/>
       <c r="BH7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="BI7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="BJ7" s="7" t="s">
         <v>34</v>
-      </c>
-      <c r="BI7" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="BJ7" s="7" t="s">
-        <v>35</v>
       </c>
       <c r="BK7" s="9"/>
       <c r="BL7" s="7" t="s">
+        <v>33</v>
+      </c>
+      <c r="BM7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="BN7" s="7" t="s">
         <v>34</v>
-      </c>
-      <c r="BM7" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="BN7" s="7" t="s">
-        <v>35</v>
       </c>
       <c r="BO7" s="9"/>
       <c r="BP7" s="11" t="s">
+        <v>33</v>
+      </c>
+      <c r="BQ7" s="7" t="s">
+        <v>26</v>
+      </c>
+      <c r="BR7" s="7" t="s">
         <v>34</v>
-      </c>
-      <c r="BQ7" s="7" t="s">
-        <v>27</v>
-      </c>
-      <c r="BR7" s="7" t="s">
-        <v>35</v>
       </c>
       <c r="BS7" s="9"/>
       <c r="BT7" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="BU7" s="7" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="8" spans="1:73" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A8" s="25"/>
       <c r="B8" s="25"/>
       <c r="C8" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="D8" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="D8" s="12" t="s">
-        <v>188</v>
-      </c>
       <c r="E8" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F8" s="14" t="s">
+        <v>35</v>
+      </c>
+      <c r="G8" s="15" t="s">
         <v>36</v>
       </c>
-      <c r="G8" s="15" t="s">
+      <c r="H8" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="H8" s="15" t="s">
+      <c r="I8" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="I8" s="15" t="s">
+      <c r="J8" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="K8" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="L8" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="M8" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="N8" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="O8" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="P8" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="Q8" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="R8" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="S8" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="T8" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="U8" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="V8" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="W8" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="X8" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="Y8" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="Z8" s="15" t="s">
+        <v>37</v>
+      </c>
+      <c r="AA8" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="AB8" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="AC8" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="J8" s="15" t="s">
+      <c r="AD8" s="15" t="s">
+        <v>38</v>
+      </c>
+      <c r="AE8" s="15" t="s">
+        <v>36</v>
+      </c>
+      <c r="AF8" s="15" t="s">
         <v>37</v>
       </c>
-      <c r="K8" s="15" t="s">
+      <c r="AG8" s="15" t="s">
         <v>38</v>
       </c>
-      <c r="L8" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="M8" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="N8" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="O8" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="P8" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="Q8" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="R8" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="S8" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="T8" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="U8" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="V8" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="W8" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="X8" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="Y8" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="Z8" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="AA8" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="AB8" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="AC8" s="15" t="s">
-        <v>40</v>
-      </c>
-      <c r="AD8" s="15" t="s">
-        <v>39</v>
-      </c>
-      <c r="AE8" s="15" t="s">
-        <v>37</v>
-      </c>
-      <c r="AF8" s="15" t="s">
-        <v>38</v>
-      </c>
-      <c r="AG8" s="15" t="s">
-        <v>39</v>
-      </c>
       <c r="AH8" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="AI8" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="AI8" s="12" t="s">
-        <v>188</v>
-      </c>
       <c r="AJ8" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AK8" s="14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AL8" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="AM8" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="AM8" s="12" t="s">
-        <v>188</v>
-      </c>
       <c r="AN8" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AO8" s="14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AP8" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="AQ8" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="AQ8" s="12" t="s">
-        <v>188</v>
-      </c>
       <c r="AR8" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AS8" s="14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AT8" s="12" t="str">
         <f>$C$8</f>
         <v>$cell_lastYear</v>
       </c>
       <c r="AU8" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AV8" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="AW8" s="14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="AX8" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="AY8" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="AY8" s="12" t="s">
-        <v>188</v>
-      </c>
       <c r="AZ8" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="BA8" s="14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="BB8" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="BC8" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="BD8" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="BE8" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="BE8" s="12" t="s">
-        <v>188</v>
-      </c>
       <c r="BF8" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="BG8" s="14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="BH8" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="BI8" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="BI8" s="12" t="s">
-        <v>188</v>
-      </c>
       <c r="BJ8" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="BK8" s="14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="BL8" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="BM8" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="BM8" s="12" t="s">
-        <v>188</v>
-      </c>
       <c r="BN8" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="BO8" s="14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="BP8" s="12" t="s">
+        <v>186</v>
+      </c>
+      <c r="BQ8" s="12" t="s">
         <v>187</v>
       </c>
-      <c r="BQ8" s="12" t="s">
-        <v>188</v>
-      </c>
       <c r="BR8" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="BS8" s="14" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="BT8" s="12" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="BU8" s="13" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="9" spans="1:73" s="5" customFormat="1" ht="20.100000000000001" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
       <c r="A9" s="16" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B9" s="17"/>
-      <c r="C9" s="28" t="s">
+      <c r="C9" s="19" t="s">
+        <v>40</v>
+      </c>
+      <c r="D9" s="19" t="s">
         <v>41</v>
       </c>
-      <c r="D9" s="28" t="s">
+      <c r="E9" s="19" t="s">
         <v>42</v>
       </c>
-      <c r="E9" s="28" t="s">
+      <c r="F9" s="19" t="s">
+        <v>163</v>
+      </c>
+      <c r="G9" s="19" t="s">
         <v>43</v>
       </c>
-      <c r="F9" s="28" t="s">
+      <c r="H9" s="19" t="s">
+        <v>44</v>
+      </c>
+      <c r="I9" s="19" t="s">
+        <v>173</v>
+      </c>
+      <c r="J9" s="19" t="s">
+        <v>45</v>
+      </c>
+      <c r="K9" s="19" t="s">
+        <v>46</v>
+      </c>
+      <c r="L9" s="19" t="s">
+        <v>174</v>
+      </c>
+      <c r="M9" s="19" t="s">
+        <v>47</v>
+      </c>
+      <c r="N9" s="19" t="s">
+        <v>48</v>
+      </c>
+      <c r="O9" s="19" t="s">
+        <v>175</v>
+      </c>
+      <c r="P9" s="19" t="s">
+        <v>49</v>
+      </c>
+      <c r="Q9" s="19" t="s">
+        <v>50</v>
+      </c>
+      <c r="R9" s="19" t="s">
+        <v>176</v>
+      </c>
+      <c r="S9" s="19" t="s">
+        <v>51</v>
+      </c>
+      <c r="T9" s="19" t="s">
+        <v>52</v>
+      </c>
+      <c r="U9" s="19" t="s">
+        <v>177</v>
+      </c>
+      <c r="V9" s="19" t="s">
+        <v>53</v>
+      </c>
+      <c r="W9" s="19" t="s">
+        <v>54</v>
+      </c>
+      <c r="X9" s="19" t="s">
+        <v>178</v>
+      </c>
+      <c r="Y9" s="19" t="s">
+        <v>55</v>
+      </c>
+      <c r="Z9" s="19" t="s">
+        <v>56</v>
+      </c>
+      <c r="AA9" s="19" t="s">
+        <v>179</v>
+      </c>
+      <c r="AB9" s="19" t="s">
+        <v>57</v>
+      </c>
+      <c r="AC9" s="19" t="s">
+        <v>58</v>
+      </c>
+      <c r="AD9" s="19" t="s">
+        <v>180</v>
+      </c>
+      <c r="AE9" s="19" t="s">
+        <v>59</v>
+      </c>
+      <c r="AF9" s="19" t="s">
+        <v>60</v>
+      </c>
+      <c r="AG9" s="19" t="s">
+        <v>181</v>
+      </c>
+      <c r="AH9" s="19" t="s">
+        <v>61</v>
+      </c>
+      <c r="AI9" s="19" t="s">
+        <v>62</v>
+      </c>
+      <c r="AJ9" s="19" t="s">
+        <v>63</v>
+      </c>
+      <c r="AK9" s="19" t="s">
         <v>164</v>
       </c>
-      <c r="G9" s="28" t="s">
-        <v>44</v>
-      </c>
-      <c r="H9" s="28" t="s">
-        <v>45</v>
-      </c>
-      <c r="I9" s="28" t="s">
-        <v>174</v>
-      </c>
-      <c r="J9" s="28" t="s">
-        <v>46</v>
-      </c>
-      <c r="K9" s="28" t="s">
-        <v>47</v>
-      </c>
-      <c r="L9" s="28" t="s">
-        <v>175</v>
-      </c>
-      <c r="M9" s="28" t="s">
-        <v>48</v>
-      </c>
-      <c r="N9" s="28" t="s">
-        <v>49</v>
-      </c>
-      <c r="O9" s="28" t="s">
-        <v>176</v>
-      </c>
-      <c r="P9" s="28" t="s">
-        <v>50</v>
-      </c>
-      <c r="Q9" s="28" t="s">
-        <v>51</v>
-      </c>
-      <c r="R9" s="28" t="s">
-        <v>177</v>
-      </c>
-      <c r="S9" s="28" t="s">
-        <v>52</v>
-      </c>
-      <c r="T9" s="28" t="s">
-        <v>53</v>
-      </c>
-      <c r="U9" s="28" t="s">
-        <v>178</v>
-      </c>
-      <c r="V9" s="28" t="s">
-        <v>54</v>
-      </c>
-      <c r="W9" s="28" t="s">
-        <v>55</v>
-      </c>
-      <c r="X9" s="28" t="s">
-        <v>179</v>
-      </c>
-      <c r="Y9" s="28" t="s">
-        <v>56</v>
-      </c>
-      <c r="Z9" s="28" t="s">
-        <v>57</v>
-      </c>
-      <c r="AA9" s="28" t="s">
-        <v>180</v>
-      </c>
-      <c r="AB9" s="28" t="s">
-        <v>58</v>
-      </c>
-      <c r="AC9" s="28" t="s">
-        <v>59</v>
-      </c>
-      <c r="AD9" s="28" t="s">
-        <v>181</v>
-      </c>
-      <c r="AE9" s="28" t="s">
-        <v>60</v>
-      </c>
-      <c r="AF9" s="28" t="s">
-        <v>61</v>
-      </c>
-      <c r="AG9" s="28" t="s">
+      <c r="AL9" s="19" t="s">
+        <v>64</v>
+      </c>
+      <c r="AM9" s="19" t="s">
+        <v>65</v>
+      </c>
+      <c r="AN9" s="19" t="s">
+        <v>66</v>
+      </c>
+      <c r="AO9" s="19" t="s">
+        <v>165</v>
+      </c>
+      <c r="AP9" s="19" t="s">
+        <v>67</v>
+      </c>
+      <c r="AQ9" s="19" t="s">
+        <v>68</v>
+      </c>
+      <c r="AR9" s="19" t="s">
+        <v>69</v>
+      </c>
+      <c r="AS9" s="19" t="s">
+        <v>166</v>
+      </c>
+      <c r="AT9" s="19" t="s">
+        <v>70</v>
+      </c>
+      <c r="AU9" s="19" t="s">
+        <v>71</v>
+      </c>
+      <c r="AV9" s="19" t="s">
+        <v>72</v>
+      </c>
+      <c r="AW9" s="19" t="s">
+        <v>167</v>
+      </c>
+      <c r="AX9" s="19" t="s">
+        <v>73</v>
+      </c>
+      <c r="AY9" s="19" t="s">
+        <v>74</v>
+      </c>
+      <c r="AZ9" s="19" t="s">
+        <v>75</v>
+      </c>
+      <c r="BA9" s="19" t="s">
+        <v>168</v>
+      </c>
+      <c r="BB9" s="19" t="s">
+        <v>76</v>
+      </c>
+      <c r="BC9" s="19" t="s">
+        <v>77</v>
+      </c>
+      <c r="BD9" s="19" t="s">
+        <v>78</v>
+      </c>
+      <c r="BE9" s="19" t="s">
+        <v>79</v>
+      </c>
+      <c r="BF9" s="19" t="s">
+        <v>80</v>
+      </c>
+      <c r="BG9" s="19" t="s">
+        <v>169</v>
+      </c>
+      <c r="BH9" s="19" t="s">
+        <v>81</v>
+      </c>
+      <c r="BI9" s="19" t="s">
+        <v>82</v>
+      </c>
+      <c r="BJ9" s="19" t="s">
+        <v>83</v>
+      </c>
+      <c r="BK9" s="19" t="s">
+        <v>170</v>
+      </c>
+      <c r="BL9" s="19" t="s">
+        <v>84</v>
+      </c>
+      <c r="BM9" s="19" t="s">
+        <v>85</v>
+      </c>
+      <c r="BN9" s="19" t="s">
+        <v>86</v>
+      </c>
+      <c r="BO9" s="19" t="s">
+        <v>171</v>
+      </c>
+      <c r="BP9" s="19" t="s">
         <v>182</v>
       </c>
-      <c r="AH9" s="28" t="s">
-        <v>62</v>
-      </c>
-      <c r="AI9" s="28" t="s">
-        <v>63</v>
-      </c>
-      <c r="AJ9" s="28" t="s">
-        <v>64</v>
-      </c>
-      <c r="AK9" s="28" t="s">
-        <v>165</v>
-      </c>
-      <c r="AL9" s="28" t="s">
-        <v>65</v>
-      </c>
-      <c r="AM9" s="28" t="s">
-        <v>66</v>
-      </c>
-      <c r="AN9" s="28" t="s">
-        <v>67</v>
-      </c>
-      <c r="AO9" s="28" t="s">
-        <v>166</v>
-      </c>
-      <c r="AP9" s="28" t="s">
-        <v>68</v>
-      </c>
-      <c r="AQ9" s="28" t="s">
-        <v>69</v>
-      </c>
-      <c r="AR9" s="28" t="s">
-        <v>70</v>
-      </c>
-      <c r="AS9" s="28" t="s">
-        <v>167</v>
-      </c>
-      <c r="AT9" s="28" t="s">
-        <v>71</v>
-      </c>
-      <c r="AU9" s="28" t="s">
-        <v>72</v>
-      </c>
-      <c r="AV9" s="28" t="s">
-        <v>73</v>
-      </c>
-      <c r="AW9" s="28" t="s">
-        <v>168</v>
-      </c>
-      <c r="AX9" s="28" t="s">
-        <v>74</v>
-      </c>
-      <c r="AY9" s="28" t="s">
-        <v>75</v>
-      </c>
-      <c r="AZ9" s="28" t="s">
-        <v>76</v>
-      </c>
-      <c r="BA9" s="28" t="s">
-        <v>169</v>
-      </c>
-      <c r="BB9" s="28" t="s">
-        <v>77</v>
-      </c>
-      <c r="BC9" s="28" t="s">
-        <v>78</v>
-      </c>
-      <c r="BD9" s="28" t="s">
-        <v>79</v>
-      </c>
-      <c r="BE9" s="28" t="s">
-        <v>80</v>
-      </c>
-      <c r="BF9" s="28" t="s">
-        <v>81</v>
-      </c>
-      <c r="BG9" s="28" t="s">
-        <v>170</v>
-      </c>
-      <c r="BH9" s="28" t="s">
-        <v>82</v>
-      </c>
-      <c r="BI9" s="28" t="s">
-        <v>83</v>
-      </c>
-      <c r="BJ9" s="28" t="s">
-        <v>84</v>
-      </c>
-      <c r="BK9" s="28" t="s">
-        <v>171</v>
-      </c>
-      <c r="BL9" s="28" t="s">
-        <v>85</v>
-      </c>
-      <c r="BM9" s="28" t="s">
-        <v>86</v>
-      </c>
-      <c r="BN9" s="28" t="s">
+      <c r="BQ9" s="19" t="s">
+        <v>183</v>
+      </c>
+      <c r="BR9" s="19" t="s">
+        <v>184</v>
+      </c>
+      <c r="BS9" s="19" t="s">
+        <v>172</v>
+      </c>
+      <c r="BT9" s="19" t="s">
         <v>87</v>
       </c>
-      <c r="BO9" s="28" t="s">
-        <v>172</v>
-      </c>
-      <c r="BP9" s="28" t="s">
-        <v>183</v>
-      </c>
-      <c r="BQ9" s="28" t="s">
-        <v>184</v>
-      </c>
-      <c r="BR9" s="28" t="s">
-        <v>185</v>
-      </c>
-      <c r="BS9" s="28" t="s">
-        <v>173</v>
-      </c>
-      <c r="BT9" s="28" t="s">
+      <c r="BU9" s="20" t="s">
         <v>88</v>
-      </c>
-      <c r="BU9" s="29" t="s">
-        <v>89</v>
       </c>
     </row>
     <row r="10" spans="1:73" s="4" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A10" s="18" t="s">
+        <v>90</v>
+      </c>
+      <c r="B10" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="B10" s="18" t="s">
+      <c r="C10" s="21" t="s">
         <v>92</v>
       </c>
-      <c r="C10" s="30" t="s">
+      <c r="D10" s="21" t="s">
         <v>93</v>
       </c>
-      <c r="D10" s="30" t="s">
+      <c r="E10" s="21" t="s">
         <v>94</v>
       </c>
-      <c r="E10" s="30" t="s">
+      <c r="F10" s="21" t="s">
         <v>95</v>
       </c>
-      <c r="F10" s="30" t="s">
+      <c r="G10" s="21" t="s">
         <v>96</v>
       </c>
-      <c r="G10" s="30" t="s">
+      <c r="H10" s="21" t="s">
         <v>97</v>
       </c>
-      <c r="H10" s="30" t="s">
+      <c r="I10" s="21" t="s">
         <v>98</v>
       </c>
-      <c r="I10" s="30" t="s">
+      <c r="J10" s="21" t="s">
         <v>99</v>
       </c>
-      <c r="J10" s="30" t="s">
+      <c r="K10" s="21" t="s">
         <v>100</v>
       </c>
-      <c r="K10" s="30" t="s">
+      <c r="L10" s="21" t="s">
         <v>101</v>
       </c>
-      <c r="L10" s="30" t="s">
+      <c r="M10" s="21" t="s">
         <v>102</v>
       </c>
-      <c r="M10" s="30" t="s">
+      <c r="N10" s="21" t="s">
         <v>103</v>
       </c>
-      <c r="N10" s="30" t="s">
+      <c r="O10" s="21" t="s">
         <v>104</v>
       </c>
-      <c r="O10" s="30" t="s">
+      <c r="P10" s="21" t="s">
         <v>105</v>
       </c>
-      <c r="P10" s="30" t="s">
+      <c r="Q10" s="21" t="s">
         <v>106</v>
       </c>
-      <c r="Q10" s="30" t="s">
+      <c r="R10" s="21" t="s">
         <v>107</v>
       </c>
-      <c r="R10" s="30" t="s">
+      <c r="S10" s="21" t="s">
         <v>108</v>
       </c>
-      <c r="S10" s="30" t="s">
+      <c r="T10" s="21" t="s">
         <v>109</v>
       </c>
-      <c r="T10" s="30" t="s">
+      <c r="U10" s="21" t="s">
         <v>110</v>
       </c>
-      <c r="U10" s="30" t="s">
+      <c r="V10" s="21" t="s">
         <v>111</v>
       </c>
-      <c r="V10" s="30" t="s">
+      <c r="W10" s="21" t="s">
         <v>112</v>
       </c>
-      <c r="W10" s="30" t="s">
+      <c r="X10" s="21" t="s">
         <v>113</v>
       </c>
-      <c r="X10" s="30" t="s">
+      <c r="Y10" s="21" t="s">
         <v>114</v>
       </c>
-      <c r="Y10" s="30" t="s">
+      <c r="Z10" s="21" t="s">
         <v>115</v>
       </c>
-      <c r="Z10" s="30" t="s">
+      <c r="AA10" s="21" t="s">
         <v>116</v>
       </c>
-      <c r="AA10" s="30" t="s">
+      <c r="AB10" s="21" t="s">
         <v>117</v>
       </c>
-      <c r="AB10" s="30" t="s">
+      <c r="AC10" s="21" t="s">
         <v>118</v>
       </c>
-      <c r="AC10" s="30" t="s">
+      <c r="AD10" s="21" t="s">
         <v>119</v>
       </c>
-      <c r="AD10" s="30" t="s">
+      <c r="AE10" s="21" t="s">
         <v>120</v>
       </c>
-      <c r="AE10" s="30" t="s">
+      <c r="AF10" s="21" t="s">
         <v>121</v>
       </c>
-      <c r="AF10" s="30" t="s">
+      <c r="AG10" s="21" t="s">
         <v>122</v>
       </c>
-      <c r="AG10" s="30" t="s">
+      <c r="AH10" s="21" t="s">
         <v>123</v>
       </c>
-      <c r="AH10" s="30" t="s">
+      <c r="AI10" s="21" t="s">
         <v>124</v>
       </c>
-      <c r="AI10" s="30" t="s">
+      <c r="AJ10" s="21" t="s">
         <v>125</v>
       </c>
-      <c r="AJ10" s="30" t="s">
+      <c r="AK10" s="21" t="s">
         <v>126</v>
       </c>
-      <c r="AK10" s="30" t="s">
+      <c r="AL10" s="21" t="s">
         <v>127</v>
       </c>
-      <c r="AL10" s="30" t="s">
+      <c r="AM10" s="21" t="s">
         <v>128</v>
       </c>
-      <c r="AM10" s="30" t="s">
+      <c r="AN10" s="21" t="s">
         <v>129</v>
       </c>
-      <c r="AN10" s="30" t="s">
+      <c r="AO10" s="21" t="s">
         <v>130</v>
       </c>
-      <c r="AO10" s="30" t="s">
+      <c r="AP10" s="22" t="s">
         <v>131</v>
       </c>
-      <c r="AP10" s="31" t="s">
+      <c r="AQ10" s="22" t="s">
         <v>132</v>
       </c>
-      <c r="AQ10" s="31" t="s">
+      <c r="AR10" s="22" t="s">
         <v>133</v>
       </c>
-      <c r="AR10" s="31" t="s">
+      <c r="AS10" s="21" t="s">
         <v>134</v>
       </c>
-      <c r="AS10" s="30" t="s">
+      <c r="AT10" s="21" t="s">
         <v>135</v>
       </c>
-      <c r="AT10" s="30" t="s">
+      <c r="AU10" s="21" t="s">
         <v>136</v>
       </c>
-      <c r="AU10" s="30" t="s">
+      <c r="AV10" s="21" t="s">
         <v>137</v>
       </c>
-      <c r="AV10" s="30" t="s">
+      <c r="AW10" s="21" t="s">
         <v>138</v>
       </c>
-      <c r="AW10" s="30" t="s">
+      <c r="AX10" s="21" t="s">
         <v>139</v>
       </c>
-      <c r="AX10" s="30" t="s">
+      <c r="AY10" s="21" t="s">
         <v>140</v>
       </c>
-      <c r="AY10" s="30" t="s">
+      <c r="AZ10" s="21" t="s">
         <v>141</v>
       </c>
-      <c r="AZ10" s="30" t="s">
+      <c r="BA10" s="21" t="s">
         <v>142</v>
       </c>
-      <c r="BA10" s="30" t="s">
+      <c r="BB10" s="21" t="s">
         <v>143</v>
       </c>
-      <c r="BB10" s="30" t="s">
+      <c r="BC10" s="21" t="s">
         <v>144</v>
       </c>
-      <c r="BC10" s="30" t="s">
+      <c r="BD10" s="21" t="s">
         <v>145</v>
       </c>
-      <c r="BD10" s="30" t="s">
+      <c r="BE10" s="21" t="s">
         <v>146</v>
       </c>
-      <c r="BE10" s="30" t="s">
+      <c r="BF10" s="21" t="s">
         <v>147</v>
       </c>
-      <c r="BF10" s="30" t="s">
+      <c r="BG10" s="21" t="s">
         <v>148</v>
       </c>
-      <c r="BG10" s="30" t="s">
+      <c r="BH10" s="21" t="s">
         <v>149</v>
       </c>
-      <c r="BH10" s="30" t="s">
+      <c r="BI10" s="21" t="s">
         <v>150</v>
       </c>
-      <c r="BI10" s="30" t="s">
+      <c r="BJ10" s="21" t="s">
         <v>151</v>
       </c>
-      <c r="BJ10" s="30" t="s">
+      <c r="BK10" s="21" t="s">
         <v>152</v>
       </c>
-      <c r="BK10" s="30" t="s">
+      <c r="BL10" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="BL10" s="30" t="s">
+      <c r="BM10" s="21" t="s">
         <v>154</v>
       </c>
-      <c r="BM10" s="30" t="s">
+      <c r="BN10" s="21" t="s">
         <v>155</v>
       </c>
-      <c r="BN10" s="30" t="s">
+      <c r="BO10" s="21" t="s">
         <v>156</v>
       </c>
-      <c r="BO10" s="30" t="s">
+      <c r="BP10" s="21" t="s">
         <v>157</v>
       </c>
-      <c r="BP10" s="30" t="s">
+      <c r="BQ10" s="21" t="s">
         <v>158</v>
       </c>
-      <c r="BQ10" s="30" t="s">
+      <c r="BR10" s="21" t="s">
         <v>159</v>
       </c>
-      <c r="BR10" s="30" t="s">
+      <c r="BS10" s="21" t="s">
         <v>160</v>
       </c>
-      <c r="BS10" s="30" t="s">
+      <c r="BT10" s="21" t="s">
         <v>161</v>
       </c>
-      <c r="BT10" s="30" t="s">
+      <c r="BU10" s="21" t="s">
         <v>162</v>
-      </c>
-      <c r="BU10" s="30" t="s">
-        <v>163</v>
       </c>
     </row>
   </sheetData>
   <mergeCells count="32">
+    <mergeCell ref="AB5:AD7"/>
+    <mergeCell ref="AE5:AG7"/>
+    <mergeCell ref="AH5:BK5"/>
+    <mergeCell ref="BL5:BS5"/>
+    <mergeCell ref="BT5:BT6"/>
+    <mergeCell ref="BU5:BU6"/>
+    <mergeCell ref="AH6:AK6"/>
+    <mergeCell ref="AL6:AO6"/>
+    <mergeCell ref="AP6:AS6"/>
+    <mergeCell ref="AT6:AW6"/>
+    <mergeCell ref="BP6:BS6"/>
+    <mergeCell ref="AX6:BA6"/>
+    <mergeCell ref="BB6:BB7"/>
+    <mergeCell ref="BC6:BC7"/>
+    <mergeCell ref="BD6:BG6"/>
+    <mergeCell ref="BH6:BK6"/>
+    <mergeCell ref="BL6:BO6"/>
     <mergeCell ref="C1:L1"/>
     <mergeCell ref="C2:K2"/>
     <mergeCell ref="A5:A8"/>
@@ -2284,23 +2300,6 @@
     <mergeCell ref="S7:U7"/>
     <mergeCell ref="V7:X7"/>
     <mergeCell ref="Y7:AA7"/>
-    <mergeCell ref="BU5:BU6"/>
-    <mergeCell ref="AH6:AK6"/>
-    <mergeCell ref="AL6:AO6"/>
-    <mergeCell ref="AP6:AS6"/>
-    <mergeCell ref="AT6:AW6"/>
-    <mergeCell ref="BP6:BS6"/>
-    <mergeCell ref="AX6:BA6"/>
-    <mergeCell ref="BB6:BB7"/>
-    <mergeCell ref="BC6:BC7"/>
-    <mergeCell ref="BD6:BG6"/>
-    <mergeCell ref="BH6:BK6"/>
-    <mergeCell ref="BL6:BO6"/>
-    <mergeCell ref="AB5:AD7"/>
-    <mergeCell ref="AE5:AG7"/>
-    <mergeCell ref="AH5:BK5"/>
-    <mergeCell ref="BL5:BS5"/>
-    <mergeCell ref="BT5:BT6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/src/main/resources/templates/summaryReportForm2.xlsx
+++ b/src/main/resources/templates/summaryReportForm2.xlsx
@@ -3,7 +3,7 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="21231"/>
   <workbookPr filterPrivacy="1"/>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3AE792F9-5280-4943-A42A-445A2DD3BD40}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{703F7A18-C03C-42D9-B19C-62C194896632}" xr6:coauthVersionLast="40" xr6:coauthVersionMax="40" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -826,32 +826,32 @@
     <xf numFmtId="164" fontId="6" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center"/>
     </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="49" fontId="5" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="49" fontId="6" fillId="0" borderId="1" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1145,18 +1145,18 @@
   </cols>
   <sheetData>
     <row r="1" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="C1" s="23" t="s">
+      <c r="C1" s="28" t="s">
         <v>0</v>
       </c>
-      <c r="D1" s="23"/>
-      <c r="E1" s="23"/>
-      <c r="F1" s="23"/>
-      <c r="G1" s="23"/>
-      <c r="H1" s="23"/>
-      <c r="I1" s="23"/>
-      <c r="J1" s="23"/>
-      <c r="K1" s="23"/>
-      <c r="L1" s="23"/>
+      <c r="D1" s="28"/>
+      <c r="E1" s="28"/>
+      <c r="F1" s="28"/>
+      <c r="G1" s="28"/>
+      <c r="H1" s="28"/>
+      <c r="I1" s="28"/>
+      <c r="J1" s="28"/>
+      <c r="K1" s="28"/>
+      <c r="L1" s="28"/>
       <c r="M1" s="1"/>
       <c r="N1" s="1"/>
       <c r="O1" s="1"/>
@@ -1198,17 +1198,17 @@
       <c r="AY1" s="1"/>
     </row>
     <row r="2" spans="1:73" x14ac:dyDescent="0.25">
-      <c r="C2" s="23" t="s">
+      <c r="C2" s="28" t="s">
         <v>1</v>
       </c>
-      <c r="D2" s="23"/>
-      <c r="E2" s="23"/>
-      <c r="F2" s="23"/>
-      <c r="G2" s="23"/>
-      <c r="H2" s="23"/>
-      <c r="I2" s="23"/>
-      <c r="J2" s="23"/>
-      <c r="K2" s="23"/>
+      <c r="D2" s="28"/>
+      <c r="E2" s="28"/>
+      <c r="F2" s="28"/>
+      <c r="G2" s="28"/>
+      <c r="H2" s="28"/>
+      <c r="I2" s="28"/>
+      <c r="J2" s="28"/>
+      <c r="K2" s="28"/>
       <c r="L2" s="1"/>
       <c r="M2" s="1"/>
       <c r="N2" s="1"/>
@@ -1260,204 +1260,204 @@
       </c>
     </row>
     <row r="5" spans="1:73" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A5" s="24" t="s">
+      <c r="A5" s="27" t="s">
         <v>3</v>
       </c>
-      <c r="B5" s="24" t="s">
+      <c r="B5" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C5" s="26" t="s">
+      <c r="C5" s="30" t="s">
         <v>5</v>
       </c>
-      <c r="D5" s="26"/>
-      <c r="E5" s="26"/>
-      <c r="F5" s="26"/>
-      <c r="G5" s="27" t="s">
+      <c r="D5" s="30"/>
+      <c r="E5" s="30"/>
+      <c r="F5" s="30"/>
+      <c r="G5" s="24" t="s">
         <v>6</v>
       </c>
-      <c r="H5" s="27"/>
-      <c r="I5" s="27"/>
-      <c r="J5" s="27"/>
-      <c r="K5" s="27"/>
-      <c r="L5" s="27"/>
-      <c r="M5" s="27"/>
-      <c r="N5" s="27"/>
-      <c r="O5" s="27"/>
-      <c r="P5" s="27"/>
-      <c r="Q5" s="27"/>
-      <c r="R5" s="27"/>
-      <c r="S5" s="27"/>
-      <c r="T5" s="27"/>
-      <c r="U5" s="27"/>
-      <c r="V5" s="27"/>
-      <c r="W5" s="27"/>
-      <c r="X5" s="27"/>
-      <c r="Y5" s="27"/>
-      <c r="Z5" s="27"/>
-      <c r="AA5" s="27"/>
-      <c r="AB5" s="31" t="s">
+      <c r="H5" s="24"/>
+      <c r="I5" s="24"/>
+      <c r="J5" s="24"/>
+      <c r="K5" s="24"/>
+      <c r="L5" s="24"/>
+      <c r="M5" s="24"/>
+      <c r="N5" s="24"/>
+      <c r="O5" s="24"/>
+      <c r="P5" s="24"/>
+      <c r="Q5" s="24"/>
+      <c r="R5" s="24"/>
+      <c r="S5" s="24"/>
+      <c r="T5" s="24"/>
+      <c r="U5" s="24"/>
+      <c r="V5" s="24"/>
+      <c r="W5" s="24"/>
+      <c r="X5" s="24"/>
+      <c r="Y5" s="24"/>
+      <c r="Z5" s="24"/>
+      <c r="AA5" s="24"/>
+      <c r="AB5" s="23" t="s">
         <v>7</v>
       </c>
-      <c r="AC5" s="31"/>
-      <c r="AD5" s="31"/>
-      <c r="AE5" s="27" t="s">
+      <c r="AC5" s="23"/>
+      <c r="AD5" s="23"/>
+      <c r="AE5" s="24" t="s">
         <v>8</v>
       </c>
-      <c r="AF5" s="27"/>
-      <c r="AG5" s="27"/>
-      <c r="AH5" s="30" t="s">
+      <c r="AF5" s="24"/>
+      <c r="AG5" s="24"/>
+      <c r="AH5" s="25" t="s">
         <v>9</v>
       </c>
-      <c r="AI5" s="30"/>
-      <c r="AJ5" s="30"/>
-      <c r="AK5" s="30"/>
-      <c r="AL5" s="30"/>
-      <c r="AM5" s="30"/>
-      <c r="AN5" s="30"/>
-      <c r="AO5" s="30"/>
-      <c r="AP5" s="30"/>
-      <c r="AQ5" s="30"/>
-      <c r="AR5" s="30"/>
-      <c r="AS5" s="30"/>
-      <c r="AT5" s="30"/>
-      <c r="AU5" s="30"/>
-      <c r="AV5" s="30"/>
-      <c r="AW5" s="30"/>
-      <c r="AX5" s="30"/>
-      <c r="AY5" s="30"/>
-      <c r="AZ5" s="30"/>
-      <c r="BA5" s="30"/>
-      <c r="BB5" s="30"/>
-      <c r="BC5" s="30"/>
-      <c r="BD5" s="30"/>
-      <c r="BE5" s="30"/>
-      <c r="BF5" s="30"/>
-      <c r="BG5" s="30"/>
-      <c r="BH5" s="30"/>
-      <c r="BI5" s="30"/>
-      <c r="BJ5" s="30"/>
-      <c r="BK5" s="30"/>
-      <c r="BL5" s="30" t="s">
+      <c r="AI5" s="25"/>
+      <c r="AJ5" s="25"/>
+      <c r="AK5" s="25"/>
+      <c r="AL5" s="25"/>
+      <c r="AM5" s="25"/>
+      <c r="AN5" s="25"/>
+      <c r="AO5" s="25"/>
+      <c r="AP5" s="25"/>
+      <c r="AQ5" s="25"/>
+      <c r="AR5" s="25"/>
+      <c r="AS5" s="25"/>
+      <c r="AT5" s="25"/>
+      <c r="AU5" s="25"/>
+      <c r="AV5" s="25"/>
+      <c r="AW5" s="25"/>
+      <c r="AX5" s="25"/>
+      <c r="AY5" s="25"/>
+      <c r="AZ5" s="25"/>
+      <c r="BA5" s="25"/>
+      <c r="BB5" s="25"/>
+      <c r="BC5" s="25"/>
+      <c r="BD5" s="25"/>
+      <c r="BE5" s="25"/>
+      <c r="BF5" s="25"/>
+      <c r="BG5" s="25"/>
+      <c r="BH5" s="25"/>
+      <c r="BI5" s="25"/>
+      <c r="BJ5" s="25"/>
+      <c r="BK5" s="25"/>
+      <c r="BL5" s="25" t="s">
         <v>10</v>
       </c>
-      <c r="BM5" s="30"/>
-      <c r="BN5" s="30"/>
-      <c r="BO5" s="30"/>
-      <c r="BP5" s="30"/>
-      <c r="BQ5" s="30"/>
-      <c r="BR5" s="30"/>
-      <c r="BS5" s="30"/>
-      <c r="BT5" s="29" t="s">
+      <c r="BM5" s="25"/>
+      <c r="BN5" s="25"/>
+      <c r="BO5" s="25"/>
+      <c r="BP5" s="25"/>
+      <c r="BQ5" s="25"/>
+      <c r="BR5" s="25"/>
+      <c r="BS5" s="25"/>
+      <c r="BT5" s="26" t="s">
         <v>11</v>
       </c>
-      <c r="BU5" s="29" t="s">
+      <c r="BU5" s="26" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="6" spans="1:73" s="6" customFormat="1" ht="20.100000000000001" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A6" s="24"/>
-      <c r="B6" s="24"/>
-      <c r="C6" s="26"/>
-      <c r="D6" s="26"/>
-      <c r="E6" s="26"/>
-      <c r="F6" s="26"/>
-      <c r="G6" s="27" t="s">
+      <c r="A6" s="27"/>
+      <c r="B6" s="27"/>
+      <c r="C6" s="30"/>
+      <c r="D6" s="30"/>
+      <c r="E6" s="30"/>
+      <c r="F6" s="30"/>
+      <c r="G6" s="24" t="s">
         <v>13</v>
       </c>
-      <c r="H6" s="27"/>
-      <c r="I6" s="27"/>
-      <c r="J6" s="27"/>
-      <c r="K6" s="27"/>
-      <c r="L6" s="27"/>
-      <c r="M6" s="27"/>
-      <c r="N6" s="27"/>
-      <c r="O6" s="27"/>
-      <c r="P6" s="27"/>
-      <c r="Q6" s="27"/>
-      <c r="R6" s="27"/>
-      <c r="S6" s="27" t="s">
+      <c r="H6" s="24"/>
+      <c r="I6" s="24"/>
+      <c r="J6" s="24"/>
+      <c r="K6" s="24"/>
+      <c r="L6" s="24"/>
+      <c r="M6" s="24"/>
+      <c r="N6" s="24"/>
+      <c r="O6" s="24"/>
+      <c r="P6" s="24"/>
+      <c r="Q6" s="24"/>
+      <c r="R6" s="24"/>
+      <c r="S6" s="24" t="s">
         <v>14</v>
       </c>
-      <c r="T6" s="27"/>
-      <c r="U6" s="27"/>
-      <c r="V6" s="27"/>
-      <c r="W6" s="27"/>
-      <c r="X6" s="27"/>
-      <c r="Y6" s="27"/>
-      <c r="Z6" s="27"/>
-      <c r="AA6" s="27"/>
-      <c r="AB6" s="31"/>
-      <c r="AC6" s="31"/>
-      <c r="AD6" s="31"/>
-      <c r="AE6" s="27"/>
-      <c r="AF6" s="27"/>
-      <c r="AG6" s="27"/>
-      <c r="AH6" s="30" t="s">
+      <c r="T6" s="24"/>
+      <c r="U6" s="24"/>
+      <c r="V6" s="24"/>
+      <c r="W6" s="24"/>
+      <c r="X6" s="24"/>
+      <c r="Y6" s="24"/>
+      <c r="Z6" s="24"/>
+      <c r="AA6" s="24"/>
+      <c r="AB6" s="23"/>
+      <c r="AC6" s="23"/>
+      <c r="AD6" s="23"/>
+      <c r="AE6" s="24"/>
+      <c r="AF6" s="24"/>
+      <c r="AG6" s="24"/>
+      <c r="AH6" s="25" t="s">
         <v>15</v>
       </c>
-      <c r="AI6" s="30"/>
-      <c r="AJ6" s="30"/>
-      <c r="AK6" s="30"/>
-      <c r="AL6" s="30" t="s">
+      <c r="AI6" s="25"/>
+      <c r="AJ6" s="25"/>
+      <c r="AK6" s="25"/>
+      <c r="AL6" s="25" t="s">
         <v>16</v>
       </c>
-      <c r="AM6" s="30"/>
-      <c r="AN6" s="30"/>
-      <c r="AO6" s="30"/>
-      <c r="AP6" s="30" t="s">
+      <c r="AM6" s="25"/>
+      <c r="AN6" s="25"/>
+      <c r="AO6" s="25"/>
+      <c r="AP6" s="25" t="s">
         <v>17</v>
       </c>
-      <c r="AQ6" s="30"/>
-      <c r="AR6" s="30"/>
-      <c r="AS6" s="30"/>
-      <c r="AT6" s="30" t="s">
+      <c r="AQ6" s="25"/>
+      <c r="AR6" s="25"/>
+      <c r="AS6" s="25"/>
+      <c r="AT6" s="25" t="s">
         <v>18</v>
       </c>
-      <c r="AU6" s="30"/>
-      <c r="AV6" s="30"/>
-      <c r="AW6" s="30"/>
-      <c r="AX6" s="30" t="s">
+      <c r="AU6" s="25"/>
+      <c r="AV6" s="25"/>
+      <c r="AW6" s="25"/>
+      <c r="AX6" s="25" t="s">
         <v>19</v>
       </c>
-      <c r="AY6" s="30"/>
-      <c r="AZ6" s="30"/>
-      <c r="BA6" s="30"/>
-      <c r="BB6" s="24" t="s">
+      <c r="AY6" s="25"/>
+      <c r="AZ6" s="25"/>
+      <c r="BA6" s="25"/>
+      <c r="BB6" s="27" t="s">
         <v>20</v>
       </c>
-      <c r="BC6" s="24" t="s">
+      <c r="BC6" s="27" t="s">
         <v>21</v>
       </c>
-      <c r="BD6" s="30" t="s">
+      <c r="BD6" s="25" t="s">
         <v>22</v>
       </c>
-      <c r="BE6" s="30"/>
-      <c r="BF6" s="30"/>
-      <c r="BG6" s="30"/>
-      <c r="BH6" s="30" t="s">
+      <c r="BE6" s="25"/>
+      <c r="BF6" s="25"/>
+      <c r="BG6" s="25"/>
+      <c r="BH6" s="25" t="s">
         <v>23</v>
       </c>
-      <c r="BI6" s="30"/>
-      <c r="BJ6" s="30"/>
-      <c r="BK6" s="30"/>
-      <c r="BL6" s="30" t="s">
+      <c r="BI6" s="25"/>
+      <c r="BJ6" s="25"/>
+      <c r="BK6" s="25"/>
+      <c r="BL6" s="25" t="s">
         <v>24</v>
       </c>
-      <c r="BM6" s="30"/>
-      <c r="BN6" s="30"/>
-      <c r="BO6" s="30"/>
-      <c r="BP6" s="30" t="s">
+      <c r="BM6" s="25"/>
+      <c r="BN6" s="25"/>
+      <c r="BO6" s="25"/>
+      <c r="BP6" s="25" t="s">
         <v>25</v>
       </c>
-      <c r="BQ6" s="30"/>
-      <c r="BR6" s="30"/>
-      <c r="BS6" s="30"/>
-      <c r="BT6" s="29"/>
-      <c r="BU6" s="29"/>
+      <c r="BQ6" s="25"/>
+      <c r="BR6" s="25"/>
+      <c r="BS6" s="25"/>
+      <c r="BT6" s="26"/>
+      <c r="BU6" s="26"/>
     </row>
     <row r="7" spans="1:73" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A7" s="24"/>
-      <c r="B7" s="24"/>
+      <c r="A7" s="27"/>
+      <c r="B7" s="27"/>
       <c r="C7" s="7" t="s">
         <v>33</v>
       </c>
@@ -1468,47 +1468,47 @@
         <v>27</v>
       </c>
       <c r="F7" s="8"/>
-      <c r="G7" s="28" t="s">
+      <c r="G7" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="H7" s="28"/>
-      <c r="I7" s="28"/>
-      <c r="J7" s="28" t="s">
+      <c r="H7" s="31"/>
+      <c r="I7" s="31"/>
+      <c r="J7" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="K7" s="28"/>
-      <c r="L7" s="28"/>
-      <c r="M7" s="28" t="s">
+      <c r="K7" s="31"/>
+      <c r="L7" s="31"/>
+      <c r="M7" s="31" t="s">
         <v>30</v>
       </c>
-      <c r="N7" s="28"/>
-      <c r="O7" s="28"/>
-      <c r="P7" s="28" t="s">
+      <c r="N7" s="31"/>
+      <c r="O7" s="31"/>
+      <c r="P7" s="31" t="s">
         <v>31</v>
       </c>
-      <c r="Q7" s="28"/>
-      <c r="R7" s="28"/>
-      <c r="S7" s="28" t="s">
+      <c r="Q7" s="31"/>
+      <c r="R7" s="31"/>
+      <c r="S7" s="31" t="s">
         <v>28</v>
       </c>
-      <c r="T7" s="28"/>
-      <c r="U7" s="28"/>
-      <c r="V7" s="28" t="s">
+      <c r="T7" s="31"/>
+      <c r="U7" s="31"/>
+      <c r="V7" s="31" t="s">
         <v>29</v>
       </c>
-      <c r="W7" s="28"/>
-      <c r="X7" s="28"/>
-      <c r="Y7" s="28" t="s">
+      <c r="W7" s="31"/>
+      <c r="X7" s="31"/>
+      <c r="Y7" s="31" t="s">
         <v>32</v>
       </c>
-      <c r="Z7" s="28"/>
-      <c r="AA7" s="28"/>
-      <c r="AB7" s="31"/>
-      <c r="AC7" s="31"/>
-      <c r="AD7" s="31"/>
-      <c r="AE7" s="27"/>
-      <c r="AF7" s="27"/>
-      <c r="AG7" s="27"/>
+      <c r="Z7" s="31"/>
+      <c r="AA7" s="31"/>
+      <c r="AB7" s="23"/>
+      <c r="AC7" s="23"/>
+      <c r="AD7" s="23"/>
+      <c r="AE7" s="24"/>
+      <c r="AF7" s="24"/>
+      <c r="AG7" s="24"/>
       <c r="AH7" s="7" t="s">
         <v>33</v>
       </c>
@@ -1559,8 +1559,8 @@
         <v>27</v>
       </c>
       <c r="BA7" s="9"/>
-      <c r="BB7" s="24"/>
-      <c r="BC7" s="24"/>
+      <c r="BB7" s="27"/>
+      <c r="BC7" s="27"/>
       <c r="BD7" s="7" t="s">
         <v>33</v>
       </c>
@@ -1609,8 +1609,8 @@
       </c>
     </row>
     <row r="8" spans="1:73" s="6" customFormat="1" ht="39.950000000000003" customHeight="1" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="A8" s="25"/>
-      <c r="B8" s="25"/>
+      <c r="A8" s="29"/>
+      <c r="B8" s="29"/>
       <c r="C8" s="12" t="s">
         <v>186</v>
       </c>
@@ -2268,23 +2268,6 @@
     </row>
   </sheetData>
   <mergeCells count="32">
-    <mergeCell ref="AB5:AD7"/>
-    <mergeCell ref="AE5:AG7"/>
-    <mergeCell ref="AH5:BK5"/>
-    <mergeCell ref="BL5:BS5"/>
-    <mergeCell ref="BT5:BT6"/>
-    <mergeCell ref="BU5:BU6"/>
-    <mergeCell ref="AH6:AK6"/>
-    <mergeCell ref="AL6:AO6"/>
-    <mergeCell ref="AP6:AS6"/>
-    <mergeCell ref="AT6:AW6"/>
-    <mergeCell ref="BP6:BS6"/>
-    <mergeCell ref="AX6:BA6"/>
-    <mergeCell ref="BB6:BB7"/>
-    <mergeCell ref="BC6:BC7"/>
-    <mergeCell ref="BD6:BG6"/>
-    <mergeCell ref="BH6:BK6"/>
-    <mergeCell ref="BL6:BO6"/>
     <mergeCell ref="C1:L1"/>
     <mergeCell ref="C2:K2"/>
     <mergeCell ref="A5:A8"/>
@@ -2300,6 +2283,23 @@
     <mergeCell ref="S7:U7"/>
     <mergeCell ref="V7:X7"/>
     <mergeCell ref="Y7:AA7"/>
+    <mergeCell ref="BU5:BU6"/>
+    <mergeCell ref="AH6:AK6"/>
+    <mergeCell ref="AL6:AO6"/>
+    <mergeCell ref="AP6:AS6"/>
+    <mergeCell ref="AT6:AW6"/>
+    <mergeCell ref="BP6:BS6"/>
+    <mergeCell ref="AX6:BA6"/>
+    <mergeCell ref="BB6:BB7"/>
+    <mergeCell ref="BC6:BC7"/>
+    <mergeCell ref="BD6:BG6"/>
+    <mergeCell ref="BH6:BK6"/>
+    <mergeCell ref="BL6:BO6"/>
+    <mergeCell ref="AB5:AD7"/>
+    <mergeCell ref="AE5:AG7"/>
+    <mergeCell ref="AH5:BK5"/>
+    <mergeCell ref="BL5:BS5"/>
+    <mergeCell ref="BT5:BT6"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
